--- a/docs/功能清单验收对照表.xlsx
+++ b/docs/功能清单验收对照表.xlsx
@@ -664,16 +664,16 @@
         <v>VAP（呼吸机相关性肺炎）指标自动统计功能有助于及时发现和预防VAP，改善呼吸机相关治疗质量</v>
       </c>
       <c r="E9" t="str">
-        <v>待口径</v>
+        <v>部分实现</v>
       </c>
       <c r="F9" t="str">
-        <v>quality_24「VAP例数」= PLACEHOLDER；quality_25「有创通气天数」= PLACEHOLDER；DSL 可表达</v>
+        <v>patient_tube 已含 is_not_plan_extubation 与 is_reintubation24 标记字段，导管统计页已在取数（TubeStatsMapper.java:46-48、TubeStatsService.java:76-77）</v>
       </c>
       <c r="G9" t="str">
-        <v>VAP 判定口径未定（是否需医生确诊记录参与判定）</v>
+        <v>质控中台 quality_17 非计划拔管数 / quality_18 拔管数 / quality_19 拔管后48h再插管数 仍为 PENDING_SOURCE，尚未接该源字段</v>
       </c>
       <c r="H9" t="str">
-        <v>先定口径（建议引入医生 VAP 确诊记录），再接有创通气天数源表</v>
+        <v>把导管统计已验证的 patient_tube 取数平移为 quality_17~19 表达式（源表已就绪，无需另建事件源）</v>
       </c>
       <c r="I9" t="str">
         <v>P1</v>
@@ -1215,16 +1215,16 @@
         <v>ICU非计划气管插管拔管率指标自动统计功能可评估气管插管管理的质量，促进相关流程的优化</v>
       </c>
       <c r="E28" t="str">
-        <v>待数据源</v>
+        <v>部分实现</v>
       </c>
       <c r="F28" t="str">
-        <v>quality_17 非计划拔管数 PENDING_SOURCE</v>
+        <v>非计划拔管数据已可得：patient_tube.is_not_plan_extubation 已按月聚合（TubeStatsMapper.java:46）</v>
       </c>
       <c r="G28" t="str">
-        <v>缺非计划拔管事件源（源库 icu_adverse_event_record 可能有记录）</v>
+        <v>ICU 非计划气管插管拔管率（quality_17）在中台仍为 PENDING_SOURCE；不良事件表 icu_adverse_event_record 未核</v>
       </c>
       <c r="H28" t="str">
-        <v>确认非计划拔管在不良事件表的类型编码后接入</v>
+        <v>优先复用 patient_tube 标记字段接 quality_17，分子分母口径与导管统计对齐</v>
       </c>
       <c r="I28" t="str">
         <v>P1</v>
@@ -1244,16 +1244,16 @@
         <v>ICU气管插管拔管后48h再插管率指标自动统计功能有助于评估拔管决策的准确性和患者呼吸功能恢复情况</v>
       </c>
       <c r="E29" t="str">
-        <v>待数据源</v>
+        <v>部分实现</v>
       </c>
       <c r="F29" t="str">
-        <v>quality_18/19 拔管数、48h再插管数 PENDING_SOURCE，DSL 表达式已备好</v>
+        <v>48h 再插管数据已可得：patient_tube.is_reintubation24 已按月聚合（TubeStatsMapper.java:48）</v>
       </c>
       <c r="G29" t="str">
-        <v>依赖插管/拔管事件源</v>
+        <v>quality_18 拔管数 / quality_19 拔管后48h再插管数 仍为 PENDING_SOURCE，拔管分母口径未接</v>
       </c>
       <c r="H29" t="str">
-        <v>随插管源表接入一并完成</v>
+        <v>随 quality_17 一并从 patient_tube 接数，复用导管统计同源口径</v>
       </c>
       <c r="I29" t="str">
         <v>P1</v>
@@ -1769,13 +1769,13 @@
         <v>部分实现</v>
       </c>
       <c r="F47" t="str">
-        <v>DepartmentCockpit.vue：患者流转趋势、本月质量指标卡、SOFA/APACHEⅡ 分值分布、器官支持、当前在科/今日出入科/平均住院日</v>
+        <v>驾驶舱已有「当前床位使用率」卡片（DepartmentCockpitServiceImpl.java:243 取 quality_304；CockpitSnapshot qualityCards）</v>
       </c>
       <c r="G47" t="str">
-        <v>床位使用率未落地（床位台账标记 PENDING_SOURCE，页面已留位）</v>
+        <v>医师床位比、护士床位比未落地（quality_302/303 PENDING_SOURCE，页面已留位）</v>
       </c>
       <c r="H47" t="str">
-        <v>接床位开放记录后即可点亮</v>
+        <v>接医护在岗与床位台账后补两张卡，床位使用率口径按已定 PMS 口径固化</v>
       </c>
       <c r="I47" t="str">
         <v>P1</v>
@@ -1882,16 +1882,16 @@
         <v>系统集成了设备管理模块，支持实时查看科室医疗设备的使用情况统计及分布状态，包括呼吸机、监护仪等关键设备的运行状态和维护信息，确保设备资源的高效利用</v>
       </c>
       <c r="E51" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F51" t="str">
-        <v>前端无设备相关实现（「设备」在 frontend 仅 1 处命中）；驾驶舱明确标注器官支持人数「不代表设备台数或库存」</v>
+        <v>驾驶舱已有「设备接入态势」面板（DepartmentCockpitServiceImpl.java:266 deviceOverview：呼吸机/监护仪接入台数）</v>
       </c>
       <c r="G51" t="str">
-        <v>无设备使用统计、分布状态、运行状态、维护信息；源库已有 config_device / config_large_device / patient_device_history / icu_device_maintenance_record / icu_device_check_record</v>
+        <v>无独立设备管理页：设备使用统计、分布状态、运行状态、维护信息均缺；源库 config_device / config_large_device / patient_device_history / icu_device_maintenance_record / icu_device_check_record 尚未接</v>
       </c>
       <c r="H51" t="str">
-        <v>接设备字典 + 使用历史 + 维护/巡检记录，新建设备管理页（数据源齐备，属取数+页面工作）</v>
+        <v>接设备字典 + 使用历史 + 维护巡检记录，新建设备管理页（数据源齐备，属取数加页面工作）</v>
       </c>
       <c r="I51" t="str">
         <v>P1</v>
@@ -1943,13 +1943,13 @@
         <v>未实现</v>
       </c>
       <c r="F53" t="str">
-        <v>驾驶舱无 bundle 趋势卡；bundle 数据本身已实现（fact_sepsis_bundle，脓毒症域 26 项全 IMPL）</v>
+        <v>bundle 数据齐备（fact_sepsis_bundle，脓毒症域 26 项全 IMPL），驾驶舱已展示完成人数卡（quality_31/419）</v>
       </c>
       <c r="G53" t="str">
-        <v>数据齐备，缺「近一年完成率趋势」图表</v>
+        <v>缺「近一年完成率趋势」图表；驾驶舱现口径为完成人数，未出率</v>
       </c>
       <c r="H53" t="str">
-        <v>复用 SepsisBundle 数据在驾驶舱加一张年度趋势图（低成本）</v>
+        <v>口径确认后补近 12 个月完成率趋势折线，复用质控中台结果</v>
       </c>
       <c r="I53" t="str">
         <v>P1</v>
@@ -1969,16 +1969,16 @@
         <v>为监控患者转出后的情况，系统支持查看近七天内转出ICU后48小时内重返率，帮助医疗团队评估转出决策的准确性和后续护理的质量</v>
       </c>
       <c r="E54" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F54" t="str">
-        <v>quality_22 48h重返率已 IMPL，事实层 fact_patient_stay.readmit_48h 可直接用</v>
+        <v>驾驶舱本月质量指标卡已含 quality_22（转出后48h重返率）：后端 DepartmentCockpitServiceImpl.java:151-156 组装卡片，前端 DepartmentCockpit.vue:79-87 渲染</v>
       </c>
       <c r="G54" t="str">
-        <v>驾驶舱无该卡片；缺近七天滚动窗口视图</v>
+        <v>窗口为本月，非清单要求的「近七天」滚动；无趋势视图</v>
       </c>
       <c r="H54" t="str">
-        <v>加一张 48h 重返率卡片（按近 7 天滚动），数据现成（低成本）</v>
+        <v>新增近 7 天滚动窗口卡片（fact_patient_stay.readmit_48h 可直接取数），保留本月卡</v>
       </c>
       <c r="I54" t="str">
         <v>P1</v>
@@ -2059,16 +2059,16 @@
         <v>部分实现</v>
       </c>
       <c r="F57" t="str">
-        <v>QualityMonthly.vue 已逐月列出各项指标数值（1-12 月横排）</v>
+        <v>质控分析已有单指标年度趋势折线（QualityMonthly.vue:103 指标选择，:570 echarts setOption，1-12 月）；后端 /quality/monthly 已回 12 个月序列</v>
       </c>
       <c r="G57" t="str">
-        <v>无趋势图（纯表格）；且床位使用率/医护床位比本身未落地</v>
+        <v>缺多指标对比与自定义起止日期；ICU 床位使用率、医护床位比等未落地指标暂无数据可画</v>
       </c>
       <c r="H57" t="str">
-        <v>加按月趋势图；数据源缺口同前</v>
+        <v>保留现状（原 P0 降级为 P1）；补多指标叠加与自定义区间查询即可</v>
       </c>
       <c r="I57" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="58">
@@ -2578,16 +2578,16 @@
         <v>系统支持按年度统计每个月份各类导管的使用情况，包括中心静脉导管、尿管、气管插管等，为医院感染控制提供数据支持</v>
       </c>
       <c r="E75" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F75" t="str">
-        <v>前端无导管页面（「导管」FE 仅 1 处、catheter FE 3 处，均为零散引用）；源库有 patient_tube / patient_tube_record / patient_tube_record_item / config_tube_*（含 config_tube_statistical 统计口径字典）</v>
+        <v>已有「导管统计分析」页按月统计：TubeStats.vue + TubeStatsController /api/tube/monthly + TubeStatsMapper.monthlyCounts（三管事件汇总 + 明细表）</v>
       </c>
       <c r="G75" t="str">
-        <v>整组功能无页面、无接口、无取数</v>
+        <v>无按年汇总各月视图；无年度趋势</v>
       </c>
       <c r="H75" t="str">
-        <v>新建导管统计模块：按已确认「按小时累加」口径（patient_tube_record_item 小时明细）聚合留置时长与用量</v>
+        <v>在现有页加「年度视图」，按 12 个月聚合同一 SQL</v>
       </c>
       <c r="I75" t="str">
         <v>P1</v>
@@ -2607,16 +2607,16 @@
         <v>为满足不同粒度的数据分析需求，系统支持按月查询或按年查询导管使用情况，便于进行短期和长期趋势分析</v>
       </c>
       <c r="E76" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F76" t="str">
-        <v>同上（无模块）</v>
+        <v>现仅支持按月份查询（TubeStats.vue:4 el-date-picker type=month，接口参数 yearMonth）</v>
       </c>
       <c r="G76" t="str">
-        <v>同上</v>
+        <v>无按年粒度查询</v>
       </c>
       <c r="H76" t="str">
-        <v>同一模块内提供月/年粒度切换</v>
+        <v>加年/月粒度切换，复用同一聚合 SQL</v>
       </c>
       <c r="I76" t="str">
         <v>P1</v>
@@ -2639,13 +2639,13 @@
         <v>未实现</v>
       </c>
       <c r="F77" t="str">
-        <v>源库 config_tube_* 系列已有导管类型/部位/选项字典，可直接支撑</v>
+        <v>导管归类为 Service 硬编码白名单（TubeStatsService.java:132-138 groupOf：CVC / 导尿管 / 气道导管 / 其他）</v>
       </c>
       <c r="G77" t="str">
-        <v>缺字典维护界面与动态列</v>
+        <v>无自定义添加导管类型与查询范围配置界面，新增类型需改代码</v>
       </c>
       <c r="H77" t="str">
-        <v>导管类型走字典驱动（新增类型不改代码）</v>
+        <v>把白名单改为可配置字典（导管类型 + 风险等级），页面支持勾选参与统计的类型</v>
       </c>
       <c r="I77" t="str">
         <v>P2</v>
@@ -2668,13 +2668,13 @@
         <v>未实现</v>
       </c>
       <c r="F78" t="str">
-        <v>后端已有 Excel 导出范式（QualityExportService / EasyExcel），可复用</v>
+        <v>导管统计页无导出入口（TubeStats.vue 无 export/下载逻辑，仅 el-table 展示）</v>
       </c>
       <c r="G78" t="str">
-        <v>导管模块无导出</v>
+        <v>统计结果无法导出到本地</v>
       </c>
       <c r="H78" t="str">
-        <v>随模块一并实现 Excel 导出</v>
+        <v>复用质控监汇表导出组件（xlsx 已在前端依赖内）</v>
       </c>
       <c r="I78" t="str">
         <v>P1</v>
@@ -2697,13 +2697,13 @@
         <v>未实现</v>
       </c>
       <c r="F79" t="str">
-        <v>源库 patient_tube_record_item 提供小时明细（可支撑每日使用数量与时长）</v>
+        <v>现为按月聚合（TubeStatsMapper.monthlyCounts 按 tube_code 分组，口径为事件发生月份），无按日粒度</v>
       </c>
       <c r="G79" t="str">
-        <v>无页面/接口；口径已确定按小时累加</v>
+        <v>无各类导管每日使用数量与使用时长明细</v>
       </c>
       <c r="H79" t="str">
-        <v>按日聚合：在置管小时数 + 使用数量，输出月历式每日汇总</v>
+        <v>加按日聚合查询 + 日历/表格视图，留置时长按日切分复用现有天数算法</v>
       </c>
       <c r="I79" t="str">
         <v>P1</v>
@@ -2726,13 +2726,13 @@
         <v>未实现</v>
       </c>
       <c r="F80" t="str">
-        <v>源库 config_tube_* 疑似含风险/危重等级字段（需确认字段名）</v>
+        <v>页面按三管分组展示（CVC / 导尿管 / 气道导管 / 其他，TubeStats.vue:30-56），未按危重等级分级</v>
       </c>
       <c r="G80" t="str">
-        <v>分级字段待确认；无分模块展示</v>
+        <v>无导管危重等级分模块显示，源表未定义风险等级字段</v>
       </c>
       <c r="H80" t="str">
-        <v>确认等级字段后按风险等级分组展示</v>
+        <v>定义导管风险等级字典后按等级分组渲染</v>
       </c>
       <c r="I80" t="str">
         <v>P2</v>
@@ -2755,13 +2755,13 @@
         <v>未实现</v>
       </c>
       <c r="F81" t="str">
-        <v>无模块</v>
+        <v>导管统计页为数字卡加表格，未引入图表（TubeStats.vue 无 echarts）</v>
       </c>
       <c r="G81" t="str">
-        <v>整组缺失</v>
+        <v>无各类导管插管量柱状图</v>
       </c>
       <c r="H81" t="str">
-        <v>随导管模块实现（echarts 柱状图）</v>
+        <v>复用前端已有 echarts 依赖加柱状图</v>
       </c>
       <c r="I81" t="str">
         <v>P1</v>
@@ -2781,16 +2781,16 @@
         <v>为了全面评估导管使用情况，系统支持统计年度导管插管总次数及非计划拔管次数，为质量改进提供关键指标</v>
       </c>
       <c r="E82" t="str">
-        <v>待数据源</v>
+        <v>部分实现</v>
       </c>
       <c r="F82" t="str">
-        <v>对应质控指标 quality_17 非计划拔管数 PENDING_SOURCE；源库 has patient_tube_drop_record（拔管）、icu_adverse_event_record（不良事件，可能含非计划拔管）</v>
+        <v>非计划拔管次数已按月出数（TubeStatsService.java:93-117 三管汇总含 unplannedRemoval / reintubation24h，TubeStats.vue:52-55 风险条）</v>
       </c>
       <c r="G82" t="str">
-        <v>缺插管/拔管/非计划拔管事件取数；非计划拔管判定口径需院感或护理确认</v>
+        <v>现为月度口径，无年度插管总次数与非计划拔管次数累计</v>
       </c>
       <c r="H82" t="str">
-        <v>接拔管与不良事件记录，同时回填 quality_17~19</v>
+        <v>加年度视图后即可满足（与序号 74 同一改动）</v>
       </c>
       <c r="I82" t="str">
         <v>P1</v>
@@ -2810,19 +2810,19 @@
         <v>系统以表格形式详细展示每月各类导管的使用数据，包括带入次数、置管次数、拔管次数、非计划拔管次数、带出次数等，便于医护人员进行详细分析和比较</v>
       </c>
       <c r="E83" t="str">
-        <v>未实现</v>
+        <v>已实现</v>
       </c>
       <c r="F83" t="str">
-        <v>源库表结构可支撑（带入/置管/拔管/带出可从 patient_tube_record 事件类型区分）</v>
+        <v>导管统计页已按类型列出置管 / 带入 / 本科置管 / 拔管 / 转出带出 / 非计划拔管 / 48h再插管 / 平均留置日 / 留置覆盖率（TubeStats.vue:61-89 明细表，TubeStatsService.java:67-90 组装）</v>
       </c>
       <c r="G83" t="str">
-        <v>无模块；事件类型编码需确认</v>
+        <v>—</v>
       </c>
       <c r="H83" t="str">
-        <v>按事件类型枚举输出五类次数</v>
+        <v>—</v>
       </c>
       <c r="I83" t="str">
-        <v>P1</v>
+        <v>—</v>
       </c>
     </row>
     <row r="84">
@@ -2839,16 +2839,16 @@
         <v>系统提供自定义时间区间查询功能，支持分析特定时期内三管（中心静脉导管、尿管、气管插管）的留置天数和相关感染发生率，为医院感染控制策略的制定和评估提供数据支持</v>
       </c>
       <c r="E84" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F84" t="str">
-        <v>感染发生率对应 quality_24/26/425（VAP/CRBSI/CAUTI）——全部未落地；留置天数口径已定按小时累加</v>
+        <v>三管留置天数与覆盖率已实现（TubeStatsService.java:79-89 avgDays / totalDays / daysCoverage：已拔用拔管时间、未拔用出科时间、仍在科算到月末）</v>
       </c>
       <c r="G84" t="str">
-        <v>自定义区间控件缺失 + 感染例数口径未定</v>
+        <v>无自定义起止时间区间；无感染发生率（源数据 is_infect 全为 0，Service 已用 infectionNote 明确标注不计算）</v>
       </c>
       <c r="H84" t="str">
-        <v>先定院感口径（建议以医生确诊记录为准），再一并实现</v>
+        <v>加起止日期查询；感染发生率待院感确诊录入（序号 107/109/111）后计算</v>
       </c>
       <c r="I84" t="str">
         <v>P1</v>
@@ -5014,16 +5014,16 @@
         <v>系统具备镇痛相关并发症的监测和预警功能，如呼吸抑制、谵妄等，通过设定预警阈值，及时识别潜在风险，提高患者安全性</v>
       </c>
       <c r="E159" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F159" t="str">
-        <v>未见呼吸抑制/谵妄并发症监测与阈值预警实现（谵妄 CAM-ICU 亦未实现）</v>
+        <v>CAM-ICU 谵妄评估已实现（CamPoint.java 评估项、SedationAssessMapper 取数、SedationMonitor.vue:165 展示）</v>
       </c>
       <c r="G159" t="str">
-        <v>需新增：呼吸抑制判定（呼吸频率 + 镇静深度阈值）与谵妄评估（CAM-ICU）及预警</v>
+        <v>无阈值预警规则（谵妄阳性、呼吸抑制未触发提醒）；镇痛并发症未与镇痛药剂量联动</v>
       </c>
       <c r="H159" t="str">
-        <v>先补谵妄评估量表（CAM-ICU）+ 阈值预警规则，复用现有提醒机制</v>
+        <v>加镇痛/镇静并发症阈值预警（呼吸抑制、CAM-ICU 阳性）并接入待办提醒，复用现有预警框架</v>
       </c>
       <c r="I159" t="str">
         <v>P1</v>
@@ -5213,7 +5213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I75"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -5356,16 +5356,16 @@
         <v>VAP（呼吸机相关性肺炎）指标自动统计功能有助于及时发现和预防VAP，改善呼吸机相关治疗质量</v>
       </c>
       <c r="E5" t="str">
-        <v>待口径</v>
+        <v>部分实现</v>
       </c>
       <c r="F5" t="str">
-        <v>quality_24「VAP例数」= PLACEHOLDER；quality_25「有创通气天数」= PLACEHOLDER；DSL 可表达</v>
+        <v>patient_tube 已含 is_not_plan_extubation 与 is_reintubation24 标记字段，导管统计页已在取数（TubeStatsMapper.java:46-48、TubeStatsService.java:76-77）</v>
       </c>
       <c r="G5" t="str">
-        <v>VAP 判定口径未定（是否需医生确诊记录参与判定）</v>
+        <v>质控中台 quality_17 非计划拔管数 / quality_18 拔管数 / quality_19 拔管后48h再插管数 仍为 PENDING_SOURCE，尚未接该源字段</v>
       </c>
       <c r="H5" t="str">
-        <v>先定口径（建议引入医生 VAP 确诊记录），再接有创通气天数源表</v>
+        <v>把导管统计已验证的 patient_tube 取数平移为 quality_17~19 表达式（源表已就绪，无需另建事件源）</v>
       </c>
       <c r="I5" t="str">
         <v>P1</v>
@@ -5617,16 +5617,16 @@
         <v>ICU非计划气管插管拔管率指标自动统计功能可评估气管插管管理的质量，促进相关流程的优化</v>
       </c>
       <c r="E14" t="str">
-        <v>待数据源</v>
+        <v>部分实现</v>
       </c>
       <c r="F14" t="str">
-        <v>quality_17 非计划拔管数 PENDING_SOURCE</v>
+        <v>非计划拔管数据已可得：patient_tube.is_not_plan_extubation 已按月聚合（TubeStatsMapper.java:46）</v>
       </c>
       <c r="G14" t="str">
-        <v>缺非计划拔管事件源（源库 icu_adverse_event_record 可能有记录）</v>
+        <v>ICU 非计划气管插管拔管率（quality_17）在中台仍为 PENDING_SOURCE；不良事件表 icu_adverse_event_record 未核</v>
       </c>
       <c r="H14" t="str">
-        <v>确认非计划拔管在不良事件表的类型编码后接入</v>
+        <v>优先复用 patient_tube 标记字段接 quality_17，分子分母口径与导管统计对齐</v>
       </c>
       <c r="I14" t="str">
         <v>P1</v>
@@ -5646,16 +5646,16 @@
         <v>ICU气管插管拔管后48h再插管率指标自动统计功能有助于评估拔管决策的准确性和患者呼吸功能恢复情况</v>
       </c>
       <c r="E15" t="str">
-        <v>待数据源</v>
+        <v>部分实现</v>
       </c>
       <c r="F15" t="str">
-        <v>quality_18/19 拔管数、48h再插管数 PENDING_SOURCE，DSL 表达式已备好</v>
+        <v>48h 再插管数据已可得：patient_tube.is_reintubation24 已按月聚合（TubeStatsMapper.java:48）</v>
       </c>
       <c r="G15" t="str">
-        <v>依赖插管/拔管事件源</v>
+        <v>quality_18 拔管数 / quality_19 拔管后48h再插管数 仍为 PENDING_SOURCE，拔管分母口径未接</v>
       </c>
       <c r="H15" t="str">
-        <v>随插管源表接入一并完成</v>
+        <v>随 quality_17 一并从 patient_tube 接数，复用导管统计同源口径</v>
       </c>
       <c r="I15" t="str">
         <v>P1</v>
@@ -5881,13 +5881,13 @@
         <v>部分实现</v>
       </c>
       <c r="F23" t="str">
-        <v>DepartmentCockpit.vue：患者流转趋势、本月质量指标卡、SOFA/APACHEⅡ 分值分布、器官支持、当前在科/今日出入科/平均住院日</v>
+        <v>驾驶舱已有「当前床位使用率」卡片（DepartmentCockpitServiceImpl.java:243 取 quality_304；CockpitSnapshot qualityCards）</v>
       </c>
       <c r="G23" t="str">
-        <v>床位使用率未落地（床位台账标记 PENDING_SOURCE，页面已留位）</v>
+        <v>医师床位比、护士床位比未落地（quality_302/303 PENDING_SOURCE，页面已留位）</v>
       </c>
       <c r="H23" t="str">
-        <v>接床位开放记录后即可点亮</v>
+        <v>接医护在岗与床位台账后补两张卡，床位使用率口径按已定 PMS 口径固化</v>
       </c>
       <c r="I23" t="str">
         <v>P1</v>
@@ -5965,16 +5965,16 @@
         <v>系统集成了设备管理模块，支持实时查看科室医疗设备的使用情况统计及分布状态，包括呼吸机、监护仪等关键设备的运行状态和维护信息，确保设备资源的高效利用</v>
       </c>
       <c r="E26" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F26" t="str">
-        <v>前端无设备相关实现（「设备」在 frontend 仅 1 处命中）；驾驶舱明确标注器官支持人数「不代表设备台数或库存」</v>
+        <v>驾驶舱已有「设备接入态势」面板（DepartmentCockpitServiceImpl.java:266 deviceOverview：呼吸机/监护仪接入台数）</v>
       </c>
       <c r="G26" t="str">
-        <v>无设备使用统计、分布状态、运行状态、维护信息；源库已有 config_device / config_large_device / patient_device_history / icu_device_maintenance_record / icu_device_check_record</v>
+        <v>无独立设备管理页：设备使用统计、分布状态、运行状态、维护信息均缺；源库 config_device / config_large_device / patient_device_history / icu_device_maintenance_record / icu_device_check_record 尚未接</v>
       </c>
       <c r="H26" t="str">
-        <v>接设备字典 + 使用历史 + 维护/巡检记录，新建设备管理页（数据源齐备，属取数+页面工作）</v>
+        <v>接设备字典 + 使用历史 + 维护巡检记录，新建设备管理页（数据源齐备，属取数加页面工作）</v>
       </c>
       <c r="I26" t="str">
         <v>P1</v>
@@ -5997,13 +5997,13 @@
         <v>未实现</v>
       </c>
       <c r="F27" t="str">
-        <v>驾驶舱无 bundle 趋势卡；bundle 数据本身已实现（fact_sepsis_bundle，脓毒症域 26 项全 IMPL）</v>
+        <v>bundle 数据齐备（fact_sepsis_bundle，脓毒症域 26 项全 IMPL），驾驶舱已展示完成人数卡（quality_31/419）</v>
       </c>
       <c r="G27" t="str">
-        <v>数据齐备，缺「近一年完成率趋势」图表</v>
+        <v>缺「近一年完成率趋势」图表；驾驶舱现口径为完成人数，未出率</v>
       </c>
       <c r="H27" t="str">
-        <v>复用 SepsisBundle 数据在驾驶舱加一张年度趋势图（低成本）</v>
+        <v>口径确认后补近 12 个月完成率趋势折线，复用质控中台结果</v>
       </c>
       <c r="I27" t="str">
         <v>P1</v>
@@ -6023,16 +6023,16 @@
         <v>为监控患者转出后的情况，系统支持查看近七天内转出ICU后48小时内重返率，帮助医疗团队评估转出决策的准确性和后续护理的质量</v>
       </c>
       <c r="E28" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F28" t="str">
-        <v>quality_22 48h重返率已 IMPL，事实层 fact_patient_stay.readmit_48h 可直接用</v>
+        <v>驾驶舱本月质量指标卡已含 quality_22（转出后48h重返率）：后端 DepartmentCockpitServiceImpl.java:151-156 组装卡片，前端 DepartmentCockpit.vue:79-87 渲染</v>
       </c>
       <c r="G28" t="str">
-        <v>驾驶舱无该卡片；缺近七天滚动窗口视图</v>
+        <v>窗口为本月，非清单要求的「近七天」滚动；无趋势视图</v>
       </c>
       <c r="H28" t="str">
-        <v>加一张 48h 重返率卡片（按近 7 天滚动），数据现成（低成本）</v>
+        <v>新增近 7 天滚动窗口卡片（fact_patient_stay.readmit_48h 可直接取数），保留本月卡</v>
       </c>
       <c r="I28" t="str">
         <v>P1</v>
@@ -6113,16 +6113,16 @@
         <v>部分实现</v>
       </c>
       <c r="F31" t="str">
-        <v>QualityMonthly.vue 已逐月列出各项指标数值（1-12 月横排）</v>
+        <v>质控分析已有单指标年度趋势折线（QualityMonthly.vue:103 指标选择，:570 echarts setOption，1-12 月）；后端 /quality/monthly 已回 12 个月序列</v>
       </c>
       <c r="G31" t="str">
-        <v>无趋势图（纯表格）；且床位使用率/医护床位比本身未落地</v>
+        <v>缺多指标对比与自定义起止日期；ICU 床位使用率、医护床位比等未落地指标暂无数据可画</v>
       </c>
       <c r="H31" t="str">
-        <v>加按月趋势图；数据源缺口同前</v>
+        <v>保留现状（原 P0 降级为 P1）；补多指标叠加与自定义区间查询即可</v>
       </c>
       <c r="I31" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="32">
@@ -6284,16 +6284,16 @@
         <v>系统支持按年度统计每个月份各类导管的使用情况，包括中心静脉导管、尿管、气管插管等，为医院感染控制提供数据支持</v>
       </c>
       <c r="E37" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F37" t="str">
-        <v>前端无导管页面（「导管」FE 仅 1 处、catheter FE 3 处，均为零散引用）；源库有 patient_tube / patient_tube_record / patient_tube_record_item / config_tube_*（含 config_tube_statistical 统计口径字典）</v>
+        <v>已有「导管统计分析」页按月统计：TubeStats.vue + TubeStatsController /api/tube/monthly + TubeStatsMapper.monthlyCounts（三管事件汇总 + 明细表）</v>
       </c>
       <c r="G37" t="str">
-        <v>整组功能无页面、无接口、无取数</v>
+        <v>无按年汇总各月视图；无年度趋势</v>
       </c>
       <c r="H37" t="str">
-        <v>新建导管统计模块：按已确认「按小时累加」口径（patient_tube_record_item 小时明细）聚合留置时长与用量</v>
+        <v>在现有页加「年度视图」，按 12 个月聚合同一 SQL</v>
       </c>
       <c r="I37" t="str">
         <v>P1</v>
@@ -6313,16 +6313,16 @@
         <v>为满足不同粒度的数据分析需求，系统支持按月查询或按年查询导管使用情况，便于进行短期和长期趋势分析</v>
       </c>
       <c r="E38" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F38" t="str">
-        <v>同上（无模块）</v>
+        <v>现仅支持按月份查询（TubeStats.vue:4 el-date-picker type=month，接口参数 yearMonth）</v>
       </c>
       <c r="G38" t="str">
-        <v>同上</v>
+        <v>无按年粒度查询</v>
       </c>
       <c r="H38" t="str">
-        <v>同一模块内提供月/年粒度切换</v>
+        <v>加年/月粒度切换，复用同一聚合 SQL</v>
       </c>
       <c r="I38" t="str">
         <v>P1</v>
@@ -6345,13 +6345,13 @@
         <v>未实现</v>
       </c>
       <c r="F39" t="str">
-        <v>源库 config_tube_* 系列已有导管类型/部位/选项字典，可直接支撑</v>
+        <v>导管归类为 Service 硬编码白名单（TubeStatsService.java:132-138 groupOf：CVC / 导尿管 / 气道导管 / 其他）</v>
       </c>
       <c r="G39" t="str">
-        <v>缺字典维护界面与动态列</v>
+        <v>无自定义添加导管类型与查询范围配置界面，新增类型需改代码</v>
       </c>
       <c r="H39" t="str">
-        <v>导管类型走字典驱动（新增类型不改代码）</v>
+        <v>把白名单改为可配置字典（导管类型 + 风险等级），页面支持勾选参与统计的类型</v>
       </c>
       <c r="I39" t="str">
         <v>P2</v>
@@ -6374,13 +6374,13 @@
         <v>未实现</v>
       </c>
       <c r="F40" t="str">
-        <v>后端已有 Excel 导出范式（QualityExportService / EasyExcel），可复用</v>
+        <v>导管统计页无导出入口（TubeStats.vue 无 export/下载逻辑，仅 el-table 展示）</v>
       </c>
       <c r="G40" t="str">
-        <v>导管模块无导出</v>
+        <v>统计结果无法导出到本地</v>
       </c>
       <c r="H40" t="str">
-        <v>随模块一并实现 Excel 导出</v>
+        <v>复用质控监汇表导出组件（xlsx 已在前端依赖内）</v>
       </c>
       <c r="I40" t="str">
         <v>P1</v>
@@ -6403,13 +6403,13 @@
         <v>未实现</v>
       </c>
       <c r="F41" t="str">
-        <v>源库 patient_tube_record_item 提供小时明细（可支撑每日使用数量与时长）</v>
+        <v>现为按月聚合（TubeStatsMapper.monthlyCounts 按 tube_code 分组，口径为事件发生月份），无按日粒度</v>
       </c>
       <c r="G41" t="str">
-        <v>无页面/接口；口径已确定按小时累加</v>
+        <v>无各类导管每日使用数量与使用时长明细</v>
       </c>
       <c r="H41" t="str">
-        <v>按日聚合：在置管小时数 + 使用数量，输出月历式每日汇总</v>
+        <v>加按日聚合查询 + 日历/表格视图，留置时长按日切分复用现有天数算法</v>
       </c>
       <c r="I41" t="str">
         <v>P1</v>
@@ -6432,13 +6432,13 @@
         <v>未实现</v>
       </c>
       <c r="F42" t="str">
-        <v>源库 config_tube_* 疑似含风险/危重等级字段（需确认字段名）</v>
+        <v>页面按三管分组展示（CVC / 导尿管 / 气道导管 / 其他，TubeStats.vue:30-56），未按危重等级分级</v>
       </c>
       <c r="G42" t="str">
-        <v>分级字段待确认；无分模块展示</v>
+        <v>无导管危重等级分模块显示，源表未定义风险等级字段</v>
       </c>
       <c r="H42" t="str">
-        <v>确认等级字段后按风险等级分组展示</v>
+        <v>定义导管风险等级字典后按等级分组渲染</v>
       </c>
       <c r="I42" t="str">
         <v>P2</v>
@@ -6461,13 +6461,13 @@
         <v>未实现</v>
       </c>
       <c r="F43" t="str">
-        <v>无模块</v>
+        <v>导管统计页为数字卡加表格，未引入图表（TubeStats.vue 无 echarts）</v>
       </c>
       <c r="G43" t="str">
-        <v>整组缺失</v>
+        <v>无各类导管插管量柱状图</v>
       </c>
       <c r="H43" t="str">
-        <v>随导管模块实现（echarts 柱状图）</v>
+        <v>复用前端已有 echarts 依赖加柱状图</v>
       </c>
       <c r="I43" t="str">
         <v>P1</v>
@@ -6487,16 +6487,16 @@
         <v>为了全面评估导管使用情况，系统支持统计年度导管插管总次数及非计划拔管次数，为质量改进提供关键指标</v>
       </c>
       <c r="E44" t="str">
-        <v>待数据源</v>
+        <v>部分实现</v>
       </c>
       <c r="F44" t="str">
-        <v>对应质控指标 quality_17 非计划拔管数 PENDING_SOURCE；源库 has patient_tube_drop_record（拔管）、icu_adverse_event_record（不良事件，可能含非计划拔管）</v>
+        <v>非计划拔管次数已按月出数（TubeStatsService.java:93-117 三管汇总含 unplannedRemoval / reintubation24h，TubeStats.vue:52-55 风险条）</v>
       </c>
       <c r="G44" t="str">
-        <v>缺插管/拔管/非计划拔管事件取数；非计划拔管判定口径需院感或护理确认</v>
+        <v>现为月度口径，无年度插管总次数与非计划拔管次数累计</v>
       </c>
       <c r="H44" t="str">
-        <v>接拔管与不良事件记录，同时回填 quality_17~19</v>
+        <v>加年度视图后即可满足（与序号 74 同一改动）</v>
       </c>
       <c r="I44" t="str">
         <v>P1</v>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B45" t="str">
         <v>统计分析</v>
@@ -6513,19 +6513,19 @@
         <v>导管分析</v>
       </c>
       <c r="D45" t="str">
-        <v>系统以表格形式详细展示每月各类导管的使用数据，包括带入次数、置管次数、拔管次数、非计划拔管次数、带出次数等，便于医护人员进行详细分析和比较</v>
+        <v>系统提供自定义时间区间查询功能，支持分析特定时期内三管（中心静脉导管、尿管、气管插管）的留置天数和相关感染发生率，为医院感染控制策略的制定和评估提供数据支持</v>
       </c>
       <c r="E45" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F45" t="str">
-        <v>源库表结构可支撑（带入/置管/拔管/带出可从 patient_tube_record 事件类型区分）</v>
+        <v>三管留置天数与覆盖率已实现（TubeStatsService.java:79-89 avgDays / totalDays / daysCoverage：已拔用拔管时间、未拔用出科时间、仍在科算到月末）</v>
       </c>
       <c r="G45" t="str">
-        <v>无模块；事件类型编码需确认</v>
+        <v>无自定义起止时间区间；无感染发生率（源数据 is_infect 全为 0，Service 已用 infectionNote 明确标注不计算）</v>
       </c>
       <c r="H45" t="str">
-        <v>按事件类型枚举输出五类次数</v>
+        <v>加起止日期查询；感染发生率待院感确诊录入（序号 107/109/111）后计算</v>
       </c>
       <c r="I45" t="str">
         <v>P1</v>
@@ -6533,65 +6533,65 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B46" t="str">
-        <v>统计分析</v>
+        <v>病情分析</v>
       </c>
       <c r="C46" t="str">
-        <v>导管分析</v>
+        <v>脓毒症诊断</v>
       </c>
       <c r="D46" t="str">
-        <v>系统提供自定义时间区间查询功能，支持分析特定时期内三管（中心静脉导管、尿管、气管插管）的留置天数和相关感染发生率，为医院感染控制策略的制定和评估提供数据支持</v>
+        <v>对于筛查出的高风险患者，系统能够自动发起预警，通过多种方式（如弹窗、短信、院内通讯软件等）及时通知相关医护人员，确保快速响应</v>
       </c>
       <c r="E46" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F46" t="str">
-        <v>感染发生率对应 quality_24/26/425（VAP/CRBSI/CAUTI）——全部未落地；留置天数口径已定按小时累加</v>
+        <v>评分/质控待办提醒机制存在（sql/36_workbench_score_todo_rule.sql：待办规则表 + 工作台待办）</v>
       </c>
       <c r="G46" t="str">
-        <v>自定义区间控件缺失 + 感染例数口径未定</v>
+        <v>仅站内待办/弹窗提醒；无短信、无院内通讯软件（HIS 消息）推送通道</v>
       </c>
       <c r="H46" t="str">
-        <v>先定院感口径（建议以医生确诊记录为准），再一并实现</v>
+        <v>如需短信/院内通讯推送，需对接院方消息网关（依赖集成）</v>
       </c>
       <c r="I46" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B47" t="str">
         <v>病情分析</v>
       </c>
       <c r="C47" t="str">
-        <v>脓毒症诊断</v>
+        <v>VAP呼吸机相关性肺炎</v>
       </c>
       <c r="D47" t="str">
-        <v>对于筛查出的高风险患者，系统能够自动发起预警，通过多种方式（如弹窗、短信、院内通讯软件等）及时通知相关医护人员，确保快速响应</v>
+        <v>系统支持医生对疑似呼吸机相关性肺炎（VAP）的患者进行确诊，记录诊断标准和过程</v>
       </c>
       <c r="E47" t="str">
-        <v>部分实现</v>
+        <v>未实现</v>
       </c>
       <c r="F47" t="str">
-        <v>评分/质控待办提醒机制存在（sql/36_workbench_score_todo_rule.sql：待办规则表 + 工作台待办）</v>
+        <v>全库无 VAP 确诊页面/接口/落库表（VAP 相关命中集中在质控指标定义与口径文档）</v>
       </c>
       <c r="G47" t="str">
-        <v>仅站内待办/弹窗提醒；无短信、无院内通讯软件（HIS 消息）推送通道</v>
+        <v>缺医生确诊录入入口 → 直接导致 quality_24 VAP 例数无法取数（当前 PLACEHOLDER）</v>
       </c>
       <c r="H47" t="str">
-        <v>如需短信/院内通讯推送，需对接院方消息网关（依赖集成）</v>
+        <v>复用脓毒症/ARDS 的确诊录入模式新建 VAP 确诊页与表（表结构可参考现有 diagnosis 记录），并回填 VAP 指标</v>
       </c>
       <c r="I47" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B48" t="str">
         <v>病情分析</v>
@@ -6600,19 +6600,19 @@
         <v>VAP呼吸机相关性肺炎</v>
       </c>
       <c r="D48" t="str">
-        <v>系统支持医生对疑似呼吸机相关性肺炎（VAP）的患者进行确诊，记录诊断标准和过程</v>
+        <v>当医生添加VAP确诊记录后，系统自动在质控模块中更新相关统计指标，如VAP发生率、平均发生天数等，为院内感染控制提供数据支持</v>
       </c>
       <c r="E48" t="str">
-        <v>未实现</v>
+        <v>待口径</v>
       </c>
       <c r="F48" t="str">
-        <v>全库无 VAP 确诊页面/接口/落库表（VAP 相关命中集中在质控指标定义与口径文档）</v>
+        <v>quality_24 VAP 例数 = PLACEHOLDER、quality_25 有创通气天数 = PLACEHOLDER；fact_device 已就绪</v>
       </c>
       <c r="G48" t="str">
-        <v>缺医生确诊录入入口 → 直接导致 quality_24 VAP 例数无法取数（当前 PLACEHOLDER）</v>
+        <v>确诊记录缺失 + 「VAP 例数是否以医生确诊为准」口径未定 + 有创通气天数未接源</v>
       </c>
       <c r="H48" t="str">
-        <v>复用脓毒症/ARDS 的确诊录入模式新建 VAP 确诊页与表（表结构可参考现有 diagnosis 记录），并回填 VAP 指标</v>
+        <v>确诊页落地后按「VAP 例数=医生确诊数」口径补 DSL，通气天数取呼吸机使用记录</v>
       </c>
       <c r="I48" t="str">
         <v>P1</v>
@@ -6620,28 +6620,28 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B49" t="str">
         <v>病情分析</v>
       </c>
       <c r="C49" t="str">
-        <v>VAP呼吸机相关性肺炎</v>
+        <v>CRBSI血管内管道相关血流感染</v>
       </c>
       <c r="D49" t="str">
-        <v>当医生添加VAP确诊记录后，系统自动在质控模块中更新相关统计指标，如VAP发生率、平均发生天数等，为院内感染控制提供数据支持</v>
+        <v>系统支持医生对疑似血管内管道相关血流感染（CRBSI）的患者进行确诊，记录诊断依据和结果</v>
       </c>
       <c r="E49" t="str">
-        <v>待口径</v>
+        <v>未实现</v>
       </c>
       <c r="F49" t="str">
-        <v>quality_24 VAP 例数 = PLACEHOLDER、quality_25 有创通气天数 = PLACEHOLDER；fact_device 已就绪</v>
+        <v>全库无 CRBSI 确诊页面/接口/表；仅质控指标定义中出现</v>
       </c>
       <c r="G49" t="str">
-        <v>确诊记录缺失 + 「VAP 例数是否以医生确诊为准」口径未定 + 有创通气天数未接源</v>
+        <v>缺确诊录入入口 → quality_26 CRBSI 例数 PENDING_SOURCE</v>
       </c>
       <c r="H49" t="str">
-        <v>确诊页落地后按「VAP 例数=医生确诊数」口径补 DSL，通气天数取呼吸机使用记录</v>
+        <v>与 VAP/CAUTI 同批建设「导管相关感染确诊」录入（三者可共用一套录入表单，按类型区分）</v>
       </c>
       <c r="I49" t="str">
         <v>P1</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" t="str">
         <v>病情分析</v>
@@ -6658,19 +6658,19 @@
         <v>CRBSI血管内管道相关血流感染</v>
       </c>
       <c r="D50" t="str">
-        <v>系统支持医生对疑似血管内管道相关血流感染（CRBSI）的患者进行确诊，记录诊断依据和结果</v>
+        <v>当医生添加CRBSI确诊记录后，系统自动在质控模块中更新相关统计指标，如CRBSI发生率、平均发生天数等，为导管相关感染预防提供数据依据</v>
       </c>
       <c r="E50" t="str">
-        <v>未实现</v>
+        <v>待数据源</v>
       </c>
       <c r="F50" t="str">
-        <v>全库无 CRBSI 确诊页面/接口/表；仅质控指标定义中出现</v>
+        <v>quality_26 CRBSI 例数 = PENDING_SOURCE；quality_27 血管内导管留置天数 = PLACEHOLDER；源库有 patient_cvc_record_tube</v>
       </c>
       <c r="G50" t="str">
-        <v>缺确诊录入入口 → quality_26 CRBSI 例数 PENDING_SOURCE</v>
+        <v>确诊记录缺失 + 导管留置天数未接源（源库病患CVC记录表可支撑）</v>
       </c>
       <c r="H50" t="str">
-        <v>与 VAP/CAUTI 同批建设「导管相关感染确诊」录入（三者可共用一套录入表单，按类型区分）</v>
+        <v>确诊录入 + 按小时累加口径接 CVC 留置记录（口径已确定）</v>
       </c>
       <c r="I50" t="str">
         <v>P1</v>
@@ -6678,28 +6678,28 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B51" t="str">
         <v>病情分析</v>
       </c>
       <c r="C51" t="str">
-        <v>CRBSI血管内管道相关血流感染</v>
+        <v>CAUTI尿道相关感染</v>
       </c>
       <c r="D51" t="str">
-        <v>当医生添加CRBSI确诊记录后，系统自动在质控模块中更新相关统计指标，如CRBSI发生率、平均发生天数等，为导管相关感染预防提供数据依据</v>
+        <v>系统支持医生对疑似导尿管相关尿路感染（CAUTI）的患者进行确诊，记录诊断过程和结果</v>
       </c>
       <c r="E51" t="str">
-        <v>待数据源</v>
+        <v>未实现</v>
       </c>
       <c r="F51" t="str">
-        <v>quality_26 CRBSI 例数 = PENDING_SOURCE；quality_27 血管内导管留置天数 = PLACEHOLDER；源库有 patient_cvc_record_tube</v>
+        <v>全库无 CAUTI 确诊页面/接口/表</v>
       </c>
       <c r="G51" t="str">
-        <v>确诊记录缺失 + 导管留置天数未接源（源库病患CVC记录表可支撑）</v>
+        <v>缺确诊录入入口 → quality_425 CAUTI 例数 PLACEHOLDER</v>
       </c>
       <c r="H51" t="str">
-        <v>确诊录入 + 按小时累加口径接 CVC 留置记录（口径已确定）</v>
+        <v>随导管相关感染确诊模块一并实现</v>
       </c>
       <c r="I51" t="str">
         <v>P1</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B52" t="str">
         <v>病情分析</v>
@@ -6716,19 +6716,19 @@
         <v>CAUTI尿道相关感染</v>
       </c>
       <c r="D52" t="str">
-        <v>系统支持医生对疑似导尿管相关尿路感染（CAUTI）的患者进行确诊，记录诊断过程和结果</v>
+        <v>当医生添加CAUTI确诊记录后，系统自动在质控模块中更新相关统计指标，如CAUTI发生率、平均发生天数等，为尿路感染预防和控制提供数据支持</v>
       </c>
       <c r="E52" t="str">
-        <v>未实现</v>
+        <v>待口径</v>
       </c>
       <c r="F52" t="str">
-        <v>全库无 CAUTI 确诊页面/接口/表</v>
+        <v>quality_425/426 均 PLACEHOLDER；导管留置明细源库已具备</v>
       </c>
       <c r="G52" t="str">
-        <v>缺确诊录入入口 → quality_425 CAUTI 例数 PLACEHOLDER</v>
+        <v>确诊记录缺失 + 导尿管留置天数未接源 + 分母口径需院感确认</v>
       </c>
       <c r="H52" t="str">
-        <v>随导管相关感染确诊模块一并实现</v>
+        <v>确诊录入落地 + 接导尿管留置记录（按小时累加）</v>
       </c>
       <c r="I52" t="str">
         <v>P1</v>
@@ -6736,28 +6736,28 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B53" t="str">
         <v>病情分析</v>
       </c>
       <c r="C53" t="str">
-        <v>CAUTI尿道相关感染</v>
+        <v>呼吸系统分析</v>
       </c>
       <c r="D53" t="str">
-        <v>当医生添加CAUTI确诊记录后，系统自动在质控模块中更新相关统计指标，如CAUTI发生率、平均发生天数等，为尿路感染预防和控制提供数据支持</v>
+        <v>系统提供全面的血流动力学分析功能，包括心输出量、血压、外周血管阻力等指标的实时监测和趋势分析，为循环系统管理提供数据支持</v>
       </c>
       <c r="E53" t="str">
-        <v>待口径</v>
+        <v>未实现</v>
       </c>
       <c r="F53" t="str">
-        <v>quality_425/426 均 PLACEHOLDER；导管留置明细源库已具备</v>
+        <v>全库无血流动力学分析页面/模块（心输出量、外周血管阻力、CO/SVR 关键词 0 命中；源库亦无监护仪高级参数表）</v>
       </c>
       <c r="G53" t="str">
-        <v>确诊记录缺失 + 导尿管留置天数未接源 + 分母口径需院感确认</v>
+        <v>无数据源、无页面。已确认：监护仪 CO/SVR 未入库，本项走手工录入</v>
       </c>
       <c r="H53" t="str">
-        <v>确诊录入落地 + 接导尿管留置记录（按小时累加）</v>
+        <v>新建血流动力学手工录入页（CO/CI/SVR/SVRI/PVR 等）+ 趋势分析；血压可用现有体征数据自动带出，其余手录</v>
       </c>
       <c r="I53" t="str">
         <v>P1</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B54" t="str">
         <v>病情分析</v>
@@ -6774,27 +6774,27 @@
         <v>呼吸系统分析</v>
       </c>
       <c r="D54" t="str">
-        <v>系统提供全面的血流动力学分析功能，包括心输出量、血压、外周血管阻力等指标的实时监测和趋势分析，为循环系统管理提供数据支持</v>
+        <v>系统支持活性药物分析，能够追踪和评估血管活性药物的使用情况及其对患者血流动力学的影响，辅助医生进行精准给药</v>
       </c>
       <c r="E54" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F54" t="str">
-        <v>全库无血流动力学分析页面/模块（心输出量、外周血管阻力、CO/SVR 关键词 0 命中；源库亦无监护仪高级参数表）</v>
+        <v>驾驶舱「器官支持」统计血管活性药使用人数；医嘱数据（patient_order）可用于明细</v>
       </c>
       <c r="G54" t="str">
-        <v>无数据源、无页面。已确认：监护仪 CO/SVR 未入库，本项走手工录入</v>
+        <v>无血管活性药物专项分析（种类/剂量/时长与血流动力学联动）</v>
       </c>
       <c r="H54" t="str">
-        <v>新建血流动力学手工录入页（CO/CI/SVR/SVRI/PVR 等）+ 趋势分析；血压可用现有体征数据自动带出，其余手录</v>
+        <v>基于医嘱 + 手工录入的血流动力学数据做关联分析</v>
       </c>
       <c r="I54" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B55" t="str">
         <v>病情分析</v>
@@ -6803,19 +6803,19 @@
         <v>呼吸系统分析</v>
       </c>
       <c r="D55" t="str">
-        <v>系统支持活性药物分析，能够追踪和评估血管活性药物的使用情况及其对患者血流动力学的影响，辅助医生进行精准给药</v>
+        <v>心功能分析模块支持对左心功能和右心功能的综合评估，包括射血分数、心肌收缩力等指标的动态监测，为心力衰竭的诊断和治疗提供依据</v>
       </c>
       <c r="E55" t="str">
-        <v>部分实现</v>
+        <v>未实现</v>
       </c>
       <c r="F55" t="str">
-        <v>驾驶舱「器官支持」统计血管活性药使用人数；医嘱数据（patient_order）可用于明细</v>
+        <v>全库无 EF/射血分数/心功能分析实现（FE 命中 0）</v>
       </c>
       <c r="G55" t="str">
-        <v>无血管活性药物专项分析（种类/剂量/时长与血流动力学联动）</v>
+        <v>无数据源（超声 EF 未入库）、无页面</v>
       </c>
       <c r="H55" t="str">
-        <v>基于医嘱 + 手工录入的血流动力学数据做关联分析</v>
+        <v>纳入血流动力学手工录入模块（EF 由床旁超声测得后手工录入）或对接超声报告</v>
       </c>
       <c r="I55" t="str">
         <v>P2</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B56" t="str">
         <v>病情分析</v>
@@ -6832,19 +6832,19 @@
         <v>呼吸系统分析</v>
       </c>
       <c r="D56" t="str">
-        <v>心功能分析模块支持对左心功能和右心功能的综合评估，包括射血分数、心肌收缩力等指标的动态监测，为心力衰竭的诊断和治疗提供依据</v>
+        <v>呼吸系统分析模块支持对呼吸频率、潮气量、氧合指数等关键指标的监测和分析，为机械通气策略的制定和调整提供依据</v>
       </c>
       <c r="E56" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F56" t="str">
-        <v>全库无 EF/射血分数/心功能分析实现（FE 命中 0）</v>
+        <v>ARDSMonitor.vue 含肺保护性通气依从率与呼吸参数（潮气量/PEEP/氧合）；呼吸频率在生命体征页 VitalSigns.vue</v>
       </c>
       <c r="G56" t="str">
-        <v>无数据源（超声 EF 未入库）、无页面</v>
+        <v>无独立「呼吸系统分析」页；氧合指数（P/F）趋势未单列</v>
       </c>
       <c r="H56" t="str">
-        <v>纳入血流动力学手工录入模块（EF 由床旁超声测得后手工录入）或对接超声报告</v>
+        <v>可新建呼吸系统分析页（复用 VitalSigns 与呼吸机参数数据，成本中等）</v>
       </c>
       <c r="I56" t="str">
         <v>P2</v>
@@ -6852,57 +6852,57 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B57" t="str">
         <v>病情分析</v>
       </c>
       <c r="C57" t="str">
-        <v>呼吸系统分析</v>
+        <v>感染控制分析</v>
       </c>
       <c r="D57" t="str">
-        <v>呼吸系统分析模块支持对呼吸频率、潮气量、氧合指数等关键指标的监测和分析，为机械通气策略的制定和调整提供依据</v>
+        <v>系统提供全面的感染控制分析功能，包括体温曲线、白细胞计数、降钙素原等感染指标的动态监测和趋势分析，辅助医生早期识别和控制感染</v>
       </c>
       <c r="E57" t="str">
         <v>部分实现</v>
       </c>
       <c r="F57" t="str">
-        <v>ARDSMonitor.vue 含肺保护性通气依从率与呼吸参数（潮气量/PEEP/氧合）；呼吸频率在生命体征页 VitalSigns.vue</v>
+        <v>体温曲线、WBC、PCT 数据可经 labtrend（LIS）与体征数据获取；LabTrend 支持 lab-liver / lab-coag 两类面板</v>
       </c>
       <c r="G57" t="str">
-        <v>无独立「呼吸系统分析」页；氧合指数（P/F）趋势未单列</v>
+        <v>无「感染控制分析」独立页面（无体温+WBC+PCT 联合趋势页）</v>
       </c>
       <c r="H57" t="str">
-        <v>可新建呼吸系统分析页（复用 VitalSigns 与呼吸机参数数据，成本中等）</v>
+        <v>扩展 LabTrend type 枚举增加感染面板（感染指标）+ 体温叠加，复用现有趋势框架</v>
       </c>
       <c r="I57" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B58" t="str">
         <v>病情分析</v>
       </c>
       <c r="C58" t="str">
-        <v>感染控制分析</v>
+        <v>肝肾功能分析</v>
       </c>
       <c r="D58" t="str">
-        <v>系统提供全面的感染控制分析功能，包括体温曲线、白细胞计数、降钙素原等感染指标的动态监测和趋势分析，辅助医生早期识别和控制感染</v>
+        <v>系统具备全面的肾功能分析功能，包括肌酐、尿素氮、电解质等指标的动态监测和趋势分析，为急性肾损伤的早期诊断和治疗提供支持</v>
       </c>
       <c r="E58" t="str">
         <v>部分实现</v>
       </c>
       <c r="F58" t="str">
-        <v>体温曲线、WBC、PCT 数据可经 labtrend（LIS）与体征数据获取；LabTrend 支持 lab-liver / lab-coag 两类面板</v>
+        <v>LAB_TREND_TYPES 仅有 lab-liver、lab-coag 两类；LIS 数据源齐备（patient_info_lis/config_lis_item）</v>
       </c>
       <c r="G58" t="str">
-        <v>无「感染控制分析」独立页面（无体温+WBC+PCT 联合趋势页）</v>
+        <v>缺 lab-renal 面板（肌酐/尿素氮/电解质）</v>
       </c>
       <c r="H58" t="str">
-        <v>扩展 LabTrend type 枚举增加感染面板（感染指标）+ 体温叠加，复用现有趋势框架</v>
+        <v>扩展 LabTrend 的 type 枚举新增肾功能面板即可（数据源已就绪，工作量小）</v>
       </c>
       <c r="I58" t="str">
         <v>P1</v>
@@ -6910,28 +6910,28 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B59" t="str">
         <v>病情分析</v>
       </c>
       <c r="C59" t="str">
-        <v>肝肾功能分析</v>
+        <v>营养分析</v>
       </c>
       <c r="D59" t="str">
-        <v>系统具备全面的肾功能分析功能，包括肌酐、尿素氮、电解质等指标的动态监测和趋势分析，为急性肾损伤的早期诊断和治疗提供支持</v>
+        <v>系统提供全面的营养分析功能，包括能量摄入、蛋白质摄入、微量元素等营养指标的计算和评估，为重症患者的营养支持方案制定提供依据</v>
       </c>
       <c r="E59" t="str">
         <v>部分实现</v>
       </c>
       <c r="F59" t="str">
-        <v>LAB_TREND_TYPES 仅有 lab-liver、lab-coag 两类；LIS 数据源齐备（patient_info_lis/config_lis_item）</v>
+        <v>营养分析页已存在（能量/蛋白质摄入统计）；源库营养数据（营养医嘱/喂养记录）已接</v>
       </c>
       <c r="G59" t="str">
-        <v>缺 lab-renal 面板（肌酐/尿素氮/电解质）</v>
+        <v>存在「字段对不上」问题：微量元素未覆盖；部分营养指标取数与源库字段映射需修正</v>
       </c>
       <c r="H59" t="str">
-        <v>扩展 LabTrend 的 type 枚举新增肾功能面板即可（数据源已就绪，工作量小）</v>
+        <v>核对并修正营养指标与源库字段映射，补微量元素项</v>
       </c>
       <c r="I59" t="str">
         <v>P1</v>
@@ -6939,28 +6939,28 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B60" t="str">
         <v>病情分析</v>
       </c>
       <c r="C60" t="str">
-        <v>营养分析</v>
+        <v>体温分析</v>
       </c>
       <c r="D60" t="str">
-        <v>系统提供全面的营养分析功能，包括能量摄入、蛋白质摄入、微量元素等营养指标的计算和评估，为重症患者的营养支持方案制定提供依据</v>
+        <v>系统提供全面的体温分析功能，支持多部位体温的动态监测和趋势分析，为发热管理和体温调节提供数据支持</v>
       </c>
       <c r="E60" t="str">
         <v>部分实现</v>
       </c>
       <c r="F60" t="str">
-        <v>营养分析页已存在（能量/蛋白质摄入统计）；源库营养数据（营养医嘱/喂养记录）已接</v>
+        <v>体温数据在生命体征页（VitalSigns.vue）以曲线呈现；源库有 patient_temperature_tube_record、patient_temperature_event_record（多部位）</v>
       </c>
       <c r="G60" t="str">
-        <v>存在「字段对不上」问题：微量元素未覆盖；部分营养指标取数与源库字段映射需修正</v>
+        <v>无独立体温分析页；多部位体温（腋温/肛温/膀胱温等）与体温事件（降温措施）未展开分析</v>
       </c>
       <c r="H60" t="str">
-        <v>核对并修正营养指标与源库字段映射，补微量元素项</v>
+        <v>新建体温分析页：多部位体温叠加曲线 + 体温事件标注（数据源已就绪）</v>
       </c>
       <c r="I60" t="str">
         <v>P1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" t="str">
         <v>病情分析</v>
@@ -6977,48 +6977,48 @@
         <v>体温分析</v>
       </c>
       <c r="D61" t="str">
-        <v>系统提供全面的体温分析功能，支持多部位体温的动态监测和趋势分析，为发热管理和体温调节提供数据支持</v>
+        <v>液体评分分析模块支持对患者液体状态的综合评估，包括液体入量、出量、体重变化等指标的分析，辅助医生进行精准的液体管理</v>
       </c>
       <c r="E61" t="str">
         <v>部分实现</v>
       </c>
       <c r="F61" t="str">
-        <v>体温数据在生命体征页（VitalSigns.vue）以曲线呈现；源库有 patient_temperature_tube_record、patient_temperature_event_record（多部位）</v>
+        <v>出入量趋势分析（BalanceTrend）已实现入量/出量/平衡；体重数据在体征记录中</v>
       </c>
       <c r="G61" t="str">
-        <v>无独立体温分析页；多部位体温（腋温/肛温/膀胱温等）与体温事件（降温措施）未展开分析</v>
+        <v>无「液体评分」（含体重变化）综合评估</v>
       </c>
       <c r="H61" t="str">
-        <v>新建体温分析页：多部位体温叠加曲线 + 体温事件标注（数据源已就绪）</v>
+        <v>在出入量趋势页叠加体重变化与液体评分指标</v>
       </c>
       <c r="I61" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B62" t="str">
         <v>病情分析</v>
       </c>
       <c r="C62" t="str">
-        <v>体温分析</v>
+        <v>床旁彩超</v>
       </c>
       <c r="D62" t="str">
-        <v>液体评分分析模块支持对患者液体状态的综合评估，包括液体入量、出量、体重变化等指标的分析，辅助医生进行精准的液体管理</v>
+        <v>系统集成床旁彩超教学功能，支持肺部、眼球、下腔静脉、腹部、膈肌、肾脏、心脏、血管等</v>
       </c>
       <c r="E62" t="str">
-        <v>部分实现</v>
+        <v>未实现</v>
       </c>
       <c r="F62" t="str">
-        <v>出入量趋势分析（BalanceTrend）已实现入量/出量/平衡；体重数据在体征记录中</v>
+        <v>全库无床旁彩超/超声模块（彩超、超声、ultrasound 命中 0，仅文档提及）</v>
       </c>
       <c r="G62" t="str">
-        <v>无「液体评分」（含体重变化）综合评估</v>
+        <v>8 个部位（肺/眼球/下腔静脉/腹部/膈肌/肾脏/心脏/血管）教学功能全无</v>
       </c>
       <c r="H62" t="str">
-        <v>在出入量趋势页叠加体重变化与液体评分指标</v>
+        <v>以静态内容为主新建床旁彩超教学模块（分部位切面图 + 要点说明）；如需对接超声设备图像，另需 PACS 集成</v>
       </c>
       <c r="I62" t="str">
         <v>P2</v>
@@ -7026,94 +7026,94 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" t="str">
         <v>病情分析</v>
       </c>
       <c r="C63" t="str">
-        <v>床旁彩超</v>
+        <v>镇痛评估分析</v>
       </c>
       <c r="D63" t="str">
-        <v>系统集成床旁彩超教学功能，支持肺部、眼球、下腔静脉、腹部、膈肌、肾脏、心脏、血管等</v>
+        <v>系统提供全面的镇痛评估分析功能，支持多种疼痛评分量表的应用和记录，如视觉模拟评分法（VAS）、数字评分法（NRS）等</v>
       </c>
       <c r="E63" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F63" t="str">
-        <v>全库无床旁彩超/超声模块（彩超、超声、ultrasound 命中 0，仅文档提及）</v>
+        <v>SedationMonitor.vue 已支持 NRS（数字评分法）、CPOT（重症疼痛观察工具）、RASS 镇静评估</v>
       </c>
       <c r="G63" t="str">
-        <v>8 个部位（肺/眼球/下腔静脉/腹部/膈肌/肾脏/心脏/血管）教学功能全无</v>
+        <v>VAS（视觉模拟评分法）未见实现</v>
       </c>
       <c r="H63" t="str">
-        <v>以静态内容为主新建床旁彩超教学模块（分部位切面图 + 要点说明）；如需对接超声设备图像，另需 PACS 集成</v>
+        <v>补充 VAS 量表（现有评分框架可直接扩展量表枚举）</v>
       </c>
       <c r="I63" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B64" t="str">
         <v>病情分析</v>
       </c>
       <c r="C64" t="str">
-        <v>镇痛评估分析</v>
+        <v>急性脑损伤患者意识评估分析</v>
       </c>
       <c r="D64" t="str">
-        <v>系统提供全面的镇痛评估分析功能，支持多种疼痛评分量表的应用和记录，如视觉模拟评分法（VAS）、数字评分法（NRS）等</v>
+        <v>系统提供专门的急性脑损伤患者意识评估分析功能，支持格拉斯哥昏迷量表（GCS）、瞳孔反应、肢体活动等神经系统评估指标的记录和分析</v>
       </c>
       <c r="E64" t="str">
         <v>部分实现</v>
       </c>
       <c r="F64" t="str">
-        <v>SedationMonitor.vue 已支持 NRS（数字评分法）、CPOT（重症疼痛观察工具）、RASS 镇静评估</v>
+        <v>NeuroMonitor.vue（GCS + 神志 + 瞳孔 + ICP 三卡，GCS 取自正式评分文书）</v>
       </c>
       <c r="G64" t="str">
-        <v>VAS（视觉模拟评分法）未见实现</v>
+        <v>「肢体活动」评估未见独立记录项（GCS 运动项内有，无独立肢体活动/肌力评估）</v>
       </c>
       <c r="H64" t="str">
-        <v>补充 VAS 量表（现有评分框架可直接扩展量表枚举）</v>
+        <v>如需独立肢体活动/肌力评估，扩展神经评估记录项</v>
       </c>
       <c r="I64" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B65" t="str">
         <v>病情分析</v>
       </c>
       <c r="C65" t="str">
-        <v>急性脑损伤患者意识评估分析</v>
+        <v>ARDS患者管理</v>
       </c>
       <c r="D65" t="str">
-        <v>系统提供专门的急性脑损伤患者意识评估分析功能，支持格拉斯哥昏迷量表（GCS）、瞳孔反应、肢体活动等神经系统评估指标的记录和分析</v>
+        <v>系统具备智能识别和标记中重度急性呼吸窘迫综合征（ARDS）患者的功能，基于柏林定义标准自动筛选符合条件的患者，并在系统中特别标识，以便医疗团队及时关注</v>
       </c>
       <c r="E65" t="str">
         <v>部分实现</v>
       </c>
       <c r="F65" t="str">
-        <v>NeuroMonitor.vue（GCS + 神志 + 瞳孔 + ICP 三卡，GCS 取自正式评分文书）</v>
+        <v>ARDS 专项域 8 项指标已定义但未落地；ArdsProneList.vue 维护中重度 ARDS 患者清单并特别标识</v>
       </c>
       <c r="G65" t="str">
-        <v>「肢体活动」评估未见独立记录项（GCS 运动项内有，无独立肢体活动/肌力评估）</v>
+        <v>柏林定义自动筛选规则未见明确实现（ARDSMonitor 内无筛查/柏林定义关键词）</v>
       </c>
       <c r="H65" t="str">
-        <v>如需独立肢体活动/肌力评估，扩展神经评估记录项</v>
+        <v>确认柏林定义筛选规则的实现位置；若无则按 P/F + PEEP 条件补筛查与患者列表标识</v>
       </c>
       <c r="I65" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B66" t="str">
         <v>病情分析</v>
@@ -7122,27 +7122,27 @@
         <v>ARDS患者管理</v>
       </c>
       <c r="D66" t="str">
-        <v>系统具备智能识别和标记中重度急性呼吸窘迫综合征（ARDS）患者的功能，基于柏林定义标准自动筛选符合条件的患者，并在系统中特别标识，以便医疗团队及时关注</v>
+        <v>系统提供全面的俯卧位通气实施情况记录功能，包括俯卧位开始和结束时间、持续时间等关键信息，并设置智能提醒机制，确保医护人员按时进行体位转换</v>
       </c>
       <c r="E66" t="str">
         <v>部分实现</v>
       </c>
       <c r="F66" t="str">
-        <v>ARDS 专项域 8 项指标已定义但未落地；ArdsProneList.vue 维护中重度 ARDS 患者清单并特别标识</v>
+        <v>ArdsProneRecord.vue（开始/结束时间、持续时间、签名）+ ArdsProneList.vue；待办提醒机制存在（sql/36_workbench_score_todo_rule.sql）</v>
       </c>
       <c r="G66" t="str">
-        <v>柏林定义自动筛选规则未见明确实现（ARDSMonitor 内无筛查/柏林定义关键词）</v>
+        <v>俯卧位体位转换的专项智能提醒未见实现（现有提醒是评分/待办规则）</v>
       </c>
       <c r="H66" t="str">
-        <v>确认柏林定义筛选规则的实现位置；若无则按 P/F + PEEP 条件补筛查与患者列表标识</v>
+        <v>将俯卧位时长规则纳入待办提醒（复用现有 todo 规则表）</v>
       </c>
       <c r="I66" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B67" t="str">
         <v>病情分析</v>
@@ -7151,19 +7151,19 @@
         <v>ARDS患者管理</v>
       </c>
       <c r="D67" t="str">
-        <v>系统提供全面的俯卧位通气实施情况记录功能，包括俯卧位开始和结束时间、持续时间等关键信息，并设置智能提醒机制，确保医护人员按时进行体位转换</v>
+        <v>系统支持将俯卧位通气数据与呼吸机参数进行联动分析，如氧合指数、潮气量等，全面评估俯卧位通气对患者呼吸功能的影响</v>
       </c>
       <c r="E67" t="str">
         <v>部分实现</v>
       </c>
       <c r="F67" t="str">
-        <v>ArdsProneRecord.vue（开始/结束时间、持续时间、签名）+ ArdsProneList.vue；待办提醒机制存在（sql/36_workbench_score_todo_rule.sql）</v>
+        <v>ARDSMonitor.vue 含肺保护性通气依从率（潮气量/PEEP/氧合）；俯卧位记录含氧合改善</v>
       </c>
       <c r="G67" t="str">
-        <v>俯卧位体位转换的专项智能提醒未见实现（现有提醒是评分/待办规则）</v>
+        <v>俯卧位前后氧合改善的量化对比图未见（仅记录）</v>
       </c>
       <c r="H67" t="str">
-        <v>将俯卧位时长规则纳入待办提醒（复用现有 todo 规则表）</v>
+        <v>在 ARDS 页加「俯卧位前后 P/F 对比」图</v>
       </c>
       <c r="I67" t="str">
         <v>P2</v>
@@ -7171,7 +7171,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" t="str">
         <v>病情分析</v>
@@ -7180,27 +7180,27 @@
         <v>ARDS患者管理</v>
       </c>
       <c r="D68" t="str">
-        <v>系统支持将俯卧位通气数据与呼吸机参数进行联动分析，如氧合指数、潮气量等，全面评估俯卧位通气对患者呼吸功能的影响</v>
+        <v>系统具备全院范围内的智能筛查功能，能够基于预设的临床指标自动识别可能的ARDS患者，提高早期诊断率</v>
       </c>
       <c r="E68" t="str">
-        <v>部分实现</v>
+        <v>未实现</v>
       </c>
       <c r="F68" t="str">
-        <v>ARDSMonitor.vue 含肺保护性通气依从率（潮气量/PEEP/氧合）；俯卧位记录含氧合改善</v>
+        <v>ARDSMonitor 内无筛查相关实现；ARDS 域筛查类指标未落地</v>
       </c>
       <c r="G68" t="str">
-        <v>俯卧位前后氧合改善的量化对比图未见（仅记录）</v>
+        <v>无全院 ARDS 智能筛查</v>
       </c>
       <c r="H68" t="str">
-        <v>在 ARDS 页加「俯卧位前后 P/F 对比」图</v>
+        <v>按氧合指数 + PEEP + 影像条件建立筛查规则（依赖呼吸机参数与检验数据）</v>
       </c>
       <c r="I68" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B69" t="str">
         <v>病情分析</v>
@@ -7209,56 +7209,56 @@
         <v>ARDS患者管理</v>
       </c>
       <c r="D69" t="str">
-        <v>系统具备全院范围内的智能筛查功能，能够基于预设的临床指标自动识别可能的ARDS患者，提高早期诊断率</v>
+        <v>对于筛查出的高风险ARDS患者，系统能够自动发起预警，通过多种方式及时通知相关医护人员，确保快速响应</v>
       </c>
       <c r="E69" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F69" t="str">
-        <v>ARDSMonitor 内无筛查相关实现；ARDS 域筛查类指标未落地</v>
+        <v>院内提醒机制（待办/弹窗）已存在，可承载预警</v>
       </c>
       <c r="G69" t="str">
-        <v>无全院 ARDS 智能筛查</v>
+        <v>无 ARDS 专项预警规则；无短信/院内通讯推送通道</v>
       </c>
       <c r="H69" t="str">
-        <v>按氧合指数 + PEEP + 影像条件建立筛查规则（依赖呼吸机参数与检验数据）</v>
+        <v>筛查落地后接入待办提醒；外发通道需院方消息网关</v>
       </c>
       <c r="I69" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B70" t="str">
         <v>病情分析</v>
       </c>
       <c r="C70" t="str">
-        <v>ARDS患者管理</v>
+        <v>镇痛管理</v>
       </c>
       <c r="D70" t="str">
-        <v>对于筛查出的高风险ARDS患者，系统能够自动发起预警，通过多种方式及时通知相关医护人员，确保快速响应</v>
+        <v>系统集成了多种标准化镇痛评估工具，包括视觉模拟评分法（VAS）、数字评定量表（NRS）等国际通用的疼痛评估量表，确保评估的规范性和可比性</v>
       </c>
       <c r="E70" t="str">
         <v>部分实现</v>
       </c>
       <c r="F70" t="str">
-        <v>院内提醒机制（待办/弹窗）已存在，可承载预警</v>
+        <v>SedationMonitor.vue 支持 NRS、CPOT、RASS</v>
       </c>
       <c r="G70" t="str">
-        <v>无 ARDS 专项预警规则；无短信/院内通讯推送通道</v>
+        <v>VAS 未实现</v>
       </c>
       <c r="H70" t="str">
-        <v>筛查落地后接入待办提醒；外发通道需院方消息网关</v>
+        <v>扩展量表枚举补 VAS</v>
       </c>
       <c r="I70" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B71" t="str">
         <v>病情分析</v>
@@ -7267,19 +7267,19 @@
         <v>镇痛管理</v>
       </c>
       <c r="D71" t="str">
-        <v>系统集成了多种标准化镇痛评估工具，包括视觉模拟评分法（VAS）、数字评定量表（NRS）等国际通用的疼痛评估量表，确保评估的规范性和可比性</v>
+        <v>系统提供镇痛效果与用药的关联分析功能，能够将疼痛评分与镇痛药物使用情况进行对比分析，帮助医生优化个体化镇痛方案</v>
       </c>
       <c r="E71" t="str">
-        <v>部分实现</v>
+        <v>未实现</v>
       </c>
       <c r="F71" t="str">
-        <v>SedationMonitor.vue 支持 NRS、CPOT、RASS</v>
+        <v>未见疼痛评分与镇痛医嘱的关联分析实现（评分与医嘱分属两类数据，未做关联）</v>
       </c>
       <c r="G71" t="str">
-        <v>VAS 未实现</v>
+        <v>无「疼痛评分 vs 镇痛药剂量/时点」对比分析</v>
       </c>
       <c r="H71" t="str">
-        <v>扩展量表枚举补 VAS</v>
+        <v>新建关联分析视图：评分曲线叠加镇痛药给药事件（医嘱数据已具备）</v>
       </c>
       <c r="I71" t="str">
         <v>P1</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B72" t="str">
         <v>病情分析</v>
@@ -7296,19 +7296,19 @@
         <v>镇痛管理</v>
       </c>
       <c r="D72" t="str">
-        <v>系统提供镇痛效果与用药的关联分析功能，能够将疼痛评分与镇痛药物使用情况进行对比分析，帮助医生优化个体化镇痛方案</v>
+        <v>系统具备镇痛相关并发症的监测和预警功能，如呼吸抑制、谵妄等，通过设定预警阈值，及时识别潜在风险，提高患者安全性</v>
       </c>
       <c r="E72" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F72" t="str">
-        <v>未见疼痛评分与镇痛医嘱的关联分析实现（评分与医嘱分属两类数据，未做关联）</v>
+        <v>CAM-ICU 谵妄评估已实现（CamPoint.java 评估项、SedationAssessMapper 取数、SedationMonitor.vue:165 展示）</v>
       </c>
       <c r="G72" t="str">
-        <v>无「疼痛评分 vs 镇痛药剂量/时点」对比分析</v>
+        <v>无阈值预警规则（谵妄阳性、呼吸抑制未触发提醒）；镇痛并发症未与镇痛药剂量联动</v>
       </c>
       <c r="H72" t="str">
-        <v>新建关联分析视图：评分曲线叠加镇痛药给药事件（医嘱数据已具备）</v>
+        <v>加镇痛/镇静并发症阈值预警（呼吸抑制、CAM-ICU 阳性）并接入待办提醒，复用现有预警框架</v>
       </c>
       <c r="I72" t="str">
         <v>P1</v>
@@ -7316,36 +7316,36 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B73" t="str">
         <v>病情分析</v>
       </c>
       <c r="C73" t="str">
-        <v>镇痛管理</v>
+        <v>急性脑损伤患者管理</v>
       </c>
       <c r="D73" t="str">
-        <v>系统具备镇痛相关并发症的监测和预警功能，如呼吸抑制、谵妄等，通过设定预警阈值，及时识别潜在风险，提高患者安全性</v>
+        <v>系统支持基于预设临床标准自动识别和分类急性脑损伤患者，包括创伤性脑损伤、脑卒中等，并在系统中特别标识，便于医疗团队进行针对性管理</v>
       </c>
       <c r="E73" t="str">
-        <v>未实现</v>
+        <v>部分实现</v>
       </c>
       <c r="F73" t="str">
-        <v>未见呼吸抑制/谵妄并发症监测与阈值预警实现（谵妄 CAM-ICU 亦未实现）</v>
+        <v>NeuroMonitor.vue 面向急性脑损伤患者意识评估，有患者清单与标识；质控侧有意识评估率指标（quality_307/308/423/424）</v>
       </c>
       <c r="G73" t="str">
-        <v>需新增：呼吸抑制判定（呼吸频率 + 镇静深度阈值）与谵妄评估（CAM-ICU）及预警</v>
+        <v>未见按病因（创伤性脑损伤/脑卒中）自动分类与标识</v>
       </c>
       <c r="H73" t="str">
-        <v>先补谵妄评估量表（CAM-ICU）+ 阈值预警规则，复用现有提醒机制</v>
+        <v>补病因分类标签（可基于诊断编码或手工标注）</v>
       </c>
       <c r="I73" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B74" t="str">
         <v>病情分析</v>
@@ -7354,27 +7354,27 @@
         <v>急性脑损伤患者管理</v>
       </c>
       <c r="D74" t="str">
-        <v>系统支持基于预设临床标准自动识别和分类急性脑损伤患者，包括创伤性脑损伤、脑卒中等，并在系统中特别标识，便于医疗团队进行针对性管理</v>
+        <v>系统集成了多种标准化意识评估工具，如格拉斯哥昏迷量表（GCS）、完全意识评分量表（FOUR评分）等，确保评估的全面性和准确性</v>
       </c>
       <c r="E74" t="str">
         <v>部分实现</v>
       </c>
       <c r="F74" t="str">
-        <v>NeuroMonitor.vue 面向急性脑损伤患者意识评估，有患者清单与标识；质控侧有意识评估率指标（quality_307/308/423/424）</v>
+        <v>GCS 已实现（NeuroMonitor.vue，取自正式评分文书）</v>
       </c>
       <c r="G74" t="str">
-        <v>未见按病因（创伤性脑损伤/脑卒中）自动分类与标识</v>
+        <v>FOUR 评分（完全意识评分量表）未实现</v>
       </c>
       <c r="H74" t="str">
-        <v>补病因分类标签（可基于诊断编码或手工标注）</v>
+        <v>新增 FOUR 量表（评分框架可复用）</v>
       </c>
       <c r="I74" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B75" t="str">
         <v>病情分析</v>
@@ -7383,50 +7383,21 @@
         <v>急性脑损伤患者管理</v>
       </c>
       <c r="D75" t="str">
-        <v>系统集成了多种标准化意识评估工具，如格拉斯哥昏迷量表（GCS）、完全意识评分量表（FOUR评分）等，确保评估的全面性和准确性</v>
+        <v>系统提供意识状态变化的趋势分析功能，能够生成直观的趋势图表，并设置智能预警机制，在意识状态出现异常变化时及时通知医护人员，促进早期干预</v>
       </c>
       <c r="E75" t="str">
         <v>部分实现</v>
       </c>
       <c r="F75" t="str">
-        <v>GCS 已实现（NeuroMonitor.vue，取自正式评分文书）</v>
+        <v>NeuroMonitor.vue GCS 趋势图已实现</v>
       </c>
       <c r="G75" t="str">
-        <v>FOUR 评分（完全意识评分量表）未实现</v>
+        <v>GCS 异常变化的智能预警未见实现（无阈值预警规则）</v>
       </c>
       <c r="H75" t="str">
-        <v>新增 FOUR 量表（评分框架可复用）</v>
+        <v>加 GCS 下降阈值预警（如 24h 内下降 ≥2 分）并接入待办提醒</v>
       </c>
       <c r="I75" t="str">
-        <v>P1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>162</v>
-      </c>
-      <c r="B76" t="str">
-        <v>病情分析</v>
-      </c>
-      <c r="C76" t="str">
-        <v>急性脑损伤患者管理</v>
-      </c>
-      <c r="D76" t="str">
-        <v>系统提供意识状态变化的趋势分析功能，能够生成直观的趋势图表，并设置智能预警机制，在意识状态出现异常变化时及时通知医护人员，促进早期干预</v>
-      </c>
-      <c r="E76" t="str">
-        <v>部分实现</v>
-      </c>
-      <c r="F76" t="str">
-        <v>NeuroMonitor.vue GCS 趋势图已实现</v>
-      </c>
-      <c r="G76" t="str">
-        <v>GCS 异常变化的智能预警未见实现（无阈值预警规则）</v>
-      </c>
-      <c r="H76" t="str">
-        <v>加 GCS 下降阈值预警（如 24h 内下降 ≥2 分）并接入待办提醒</v>
-      </c>
-      <c r="I76" t="str">
         <v>P2</v>
       </c>
     </row>
@@ -7484,10 +7455,10 @@
         <v>已实现</v>
       </c>
       <c r="C3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="str">
-        <v>54.3%</v>
+        <v>54.9%</v>
       </c>
     </row>
     <row r="4">
@@ -7498,10 +7469,10 @@
         <v>部分实现</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D4" t="str">
-        <v>20.1%</v>
+        <v>26.2%</v>
       </c>
     </row>
     <row r="5">
@@ -7512,10 +7483,10 @@
         <v>未实现</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D5" t="str">
-        <v>13.4%</v>
+        <v>9.1%</v>
       </c>
     </row>
     <row r="6">
@@ -7526,10 +7497,10 @@
         <v>待数据源</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6" t="str">
-        <v>8.5%</v>
+        <v>6.7%</v>
       </c>
     </row>
     <row r="7">
@@ -7540,10 +7511,10 @@
         <v>待口径</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="str">
-        <v>3.0%</v>
+        <v>2.4%</v>
       </c>
     </row>
     <row r="8">
@@ -7624,10 +7595,10 @@
         <v>P0</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="str">
-        <v>0.6%</v>
+        <v>0%</v>
       </c>
     </row>
     <row r="14">
@@ -7638,10 +7609,10 @@
         <v>P1</v>
       </c>
       <c r="C14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="str">
-        <v>32.3%</v>
+        <v>31.7%</v>
       </c>
     </row>
     <row r="15">
@@ -7677,7 +7648,7 @@
         <v>质控管理</v>
       </c>
       <c r="B18" t="str">
-        <v>24 / 6 / 0 / 11 / 3 / 1</v>
+        <v>24 / 9 / 0 / 9 / 2 / 1</v>
       </c>
       <c r="C18">
         <v>45</v>
@@ -7691,7 +7662,7 @@
         <v>统计分析</v>
       </c>
       <c r="B19" t="str">
-        <v>14 / 9 / 13 / 2 / 0 / 0</v>
+        <v>15 / 15 / 7 / 1 / 0 / 0</v>
       </c>
       <c r="C19">
         <v>38</v>
@@ -7705,7 +7676,7 @@
         <v>病情分析</v>
       </c>
       <c r="B20" t="str">
-        <v>49 / 18 / 9 / 1 / 2 / 0</v>
+        <v>49 / 19 / 8 / 1 / 2 / 0</v>
       </c>
       <c r="C20">
         <v>79</v>
@@ -7733,7 +7704,7 @@
         <v>合计</v>
       </c>
       <c r="B22" t="str">
-        <v>89 / 33 / 22 / 14 / 5 / 1</v>
+        <v>90 / 43 / 15 / 11 / 4 / 1</v>
       </c>
       <c r="C22">
         <v>164</v>

--- a/docs/功能清单验收对照表.xlsx
+++ b/docs/功能清单验收对照表.xlsx
@@ -699,17 +699,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>待数据源</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fact_dvt 已就绪，DVT 域 12 项中仅 1 项 IMPL（DVT相关死亡人数）</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>11 项待接老系统 useDvtAdviceList（药物/机械/滤器预防明细）</t>
+          <t>2026-10-15落地：fact_dvt 接医嘱侧（药物经 patient_advice_execute 关联、机械与滤器按 patient_advice_original），按「执行区间∩本周期」过滤，关键词按2024版ICU-07官方口径；患者/科室月度质控与规则层预防率（14÷403）全部出数</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -744,17 +739,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>待数据源</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>quality_17 非计划拔管数 / quality_18 拔管数 / quality_19 拔管后48h再插管数 = PENDING_SOURCE，表达式已备好</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>缺插管/拔管事件源表取数（ICU 源库有 patient_tube_record / patient_tube_drop_record）</t>
+          <t>2026-10-15落地：quality_17/18/19 接 patient_tube（非计划拔管/拔管数/48h再插管，2024版ICU-12/13口径），患者月度/科室月度/驾驶舱同步生效</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1089,17 +1079,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>待数据源</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>quality_301 开放总床日数 / quality_304 开放床位数 = PENDING_SOURCE；床位台账在驾驶舱标 PENDING_SOURCE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>缺开放床位数/床日数来源（需护理或床位管理提供）</t>
+          <t>2026-10-15落地：quality_301/304 激活（config_bed 实库验证字段），床位使用率规则 2÷301 自动出数（2024版ICU-01口径）</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1142,7 +1127,6 @@
           <t>2026-10-15连库激活：config_staff ICU相关在职医师58人（档案科室+岗位），排班表未启用故无班次过滤；医师床位比规则302÷304自动出数（2024版ICU-02口径）</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>接排班表；口径需医务科确认</t>
@@ -1183,7 +1167,6 @@
           <t>2026-10-15连库激活：config_staff ICU相关在职护士89人（护士/护师岗）；护士床位比规则303÷304自动出数（2024版ICU-03口径）</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>同上，与医师床位比一并实现</t>
@@ -1321,17 +1304,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>待数据源</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>fact_dvt 就绪；DVT 域仅 1/12 项 IMPL</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>缺 DVT 预防措施执行明细源</t>
+          <t>2026-10-15落地：同上，规则层 DVT预防率（quality_14÷quality_403×100）自动出数</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1426,17 +1404,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>需人工录入</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>quality_15 预计病死率 IMPL（引擎已引用「预计病死」）；quality_30 实际病死率 = MANUAL；标化病死指数 = 实际/预计</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>实际病死率需人工录入，否则标化病死指数无法计算</t>
+          <t>标化病死指数已自动计算：规则层「标化病死指数=quality_30÷quality_31」（rule 1483050943291009），quality_30 ICU实际病死率、quality_31 APACHEⅡ预计病死率均 IMPL（引擎取 mortality_rate 求和），重算后自动出数，无需人工录入</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1546,17 +1519,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>待数据源</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>quality_21 术后转入 IMPL；quality_20「术后非计划转入」= PENDING_SOURCE</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>缺「非计划」判定来源</t>
+          <t>2026-10-15落地：quality_20「术后非计划转入例数」接源字段 patient_info.is_plan（0=非计划转入，业务方确认），where=post_op=1 AND is_plan=0 AND admitted_in_period=1，expr_version+1 已同步入库（IMPL）；非计划转入率=quality_20÷quality_21 规则自动出数（2024版ICU-14口径）</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2391,17 +2359,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>bundle 数据齐备（fact_sepsis_bundle，脓毒症域 26 项全 IMPL），驾驶舱已展示完成人数卡（quality_31/419）</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>缺「近一年完成率趋势」图表；驾驶舱现口径为完成人数，未出率</t>
+          <t>驾驶舱「SEPSIS BUNDLE」面板：近 12 个月感染性休克 bundle 完成率折线（quality_11÷quality_10，bundleTrend 逐月 分子/分母/完成率，缺月断开不按 0）；fact_sepsis_bundle + 脓毒症域 26 项 IMPL，数据由每日批算落库</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2489,7 +2452,6 @@
           <t>2026-10-15连库激活：config_staff ICU相关在职医师58人（档案科室+岗位），排班表未启用故无班次过滤；医师床位比规则302÷304自动出数（2024版ICU-02口径）</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>接床位与排班数据后，与质控中台共用同一口径（避免两处口径漂移）</t>
@@ -2575,7 +2537,6 @@
           <t>2026-10-15连库激活：config_staff ICU相关在职医师58人（档案科室+岗位），排班表未启用故无班次过滤；医师床位比规则302÷304自动出数（2024版ICU-02口径）</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>保留现状（原 P0 降级为 P1）；补多指标叠加与自定义区间查询即可</t>
@@ -2713,19 +2674,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>时间维度只有 月/季/年 档位，无自定义起止日期；48h 重返数据已 IMPL（fact_patient_stay.readmit_48h）</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>缺自定义时间区间控件与按区间取数的接口；缺 48h 重返病例专项筛选视图</t>
-        </is>
-      </c>
+          <t>质控看板已有「自定义」周期档位（periodType=CUSTOM 起止日期，后端 PeriodRange.CUSTOM）；指标详情抽屉含患者明细四档视角（全部/分子/分母/未达标）——48h 重返（quality_22）在自定义周期下点分子即得重返病例清单（/api/quality/metric/patients），可结合患者字段分析特征</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>给质控查询加起止日期参数 + 48h 重返病例筛选入口（数据现成，成本低）</t>
@@ -2883,14 +2840,10 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Apache2Overview.vue 支持时间范围筛选，可出分布与预期死亡率</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>「实际死亡数」依赖人工录入（quality_30 实际病死率 MANUAL），未录入时标化死亡指数算不出；引擎侧「预计病死率」已 IMPL（quality_15）</t>
-        </is>
-      </c>
+          <t>2026-10-15统一组件后：Apache2 总览页接入 TimeRangeBar（本月/近30天/近90天/本年快捷档 + 任意起止日期），分布/平均预期死亡率可按任意区间分析；页内未单独展示实际死亡数与标化死亡指数（SMR 已由质控看板 quality_30/31 规则自动出数）</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>补实际死亡数录入/核对流程（或接入死亡转归字段做校验）</t>
@@ -2923,17 +2876,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SedationMonitor.vue（RASS/NRS/CPOT）、NeuroMonitor.vue（GCS/神志/瞳孔/ICP）；GCS FE=101、RASS FE=13 命中</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>ADL（日常生活活动能力）评分完全未实现（「ADL」「日常生活活动」全库 0 命中）</t>
+          <t>2026-10-15落地：GCS / RASS 已有（神经监测/镇静镇静页），ADL（Barthel 指数）新增手工录入模块（patient_doc_adl 表 + /api/adl/* + /page/hemodynamics 第二区块），十项 0/5/10/15 逐项录入、总分服务端求和、依赖四级分色 + 总分趋势图</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3193,17 +3141,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>已有「导管统计分析」页按月统计：TubeStats.vue + TubeStatsController /api/tube/monthly + TubeStatsMapper.monthlyCounts（三管事件汇总 + 明细表）</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>无按年汇总各月视图；无年度趋势</t>
+          <t>2026-10-15落地：导管统计页新增年度视图（/api/tube/yearly，12月×类型趋势图+矩阵表，口径与月度一致）+年度Excel导出</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3278,17 +3221,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>导管归类为 Service 硬编码白名单（TubeStatsService.java:132-138 groupOf：CVC / 导尿管 / 气道导管 / 其他）</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>无自定义添加导管类型与查询范围配置界面，新增类型需改代码</t>
+          <t>2026-10-15落地：新增 config_tube_group 配置表（sql/53）+ /api/tube/groups 接口 + 导管统计页「导管类型管理」弹窗，任意 tube_code 可归入自定义分组并标注危重等级，归类优先级=配置&gt;系统默认白名单&gt;其他，保存后统计即时生效</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3363,17 +3301,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>现为按月聚合（TubeStatsMapper.monthlyCounts 按 tube_code 分组，口径为事件发生月份），无按日粒度</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>无各类导管每日使用数量与使用时长明细</t>
+          <t>2026-10-15落地：导管统计页新增「按日」视图（/api/tube/daily + TubeStatsMapper.dailyRows），按「日 × 导管分组」展示每天新置管/拔管/带出/非计划拔管/24h再插管，未拔导管算至月末；月度/年度/按日三视图可切</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3408,17 +3341,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>部分实现</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>页面按三管分组展示（CVC / 导尿管 / 气道导管 / 其他，TubeStats.vue:30-56），未按危重等级分级</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>无导管危重等级分模块显示，源表未定义风险等级字段</t>
+          <t>2026-10-15落地：月度明细与导管类型管理均带危重等级标注（高/中/低，配置优先，默认气道/CVC=高、导尿管=中、其余=低）；「按危重等级分模块置顶展示」未做，如需可基于 riskLevel 字段扩展</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3453,17 +3381,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>导管统计页为数字卡加表格，未引入图表（TubeStats.vue 无 echarts）</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>无各类导管插管量柱状图</t>
+          <t>2026-10-15落地：年度视图含按月堆叠柱状图（echarts，按导管类型分色）</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3498,17 +3421,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>非计划拔管次数已按月出数（TubeStatsService.java:93-117 三管汇总含 unplannedRemoval / reintubation24h，TubeStats.vue:52-55 风险条）</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>现为月度口径，无年度插管总次数与非计划拔管次数累计</t>
+          <t>2026-10-15落地：年度视图含全年汇总（yearSum：置管/拔管/非计划/再插管）</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3588,19 +3506,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>三管留置天数与覆盖率已实现（TubeStatsService.java:79-89 avgDays / totalDays / daysCoverage：已拔用拔管时间、未拔用出科时间、仍在科算到月末）</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>无自定义起止时间区间；无感染发生率（源数据 is_infect 全为 0，Service 已用 infectionNote 明确标注不计算）</t>
-        </is>
-      </c>
+          <t>2026-10-15落地：导管统计按日视图支持自定义起止区间（TimeRangeBar，本月/近7天/近30天/本年快捷档，后端 /api/tube/daily startDate/endDate，上限92天），日粒度统计三管新置/拔管/带出/非计划/24h再插管/在管数；留置天数与感染口径在月度视图（avgDays/totalDays/感染说明）</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>加起止日期查询；感染发生率待院感确诊录入（序号 107/109/111）后计算</t>
@@ -4578,17 +4492,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>全库无血流动力学分析页面/模块（心输出量、外周血管阻力、CO/SVR 关键词 0 命中；源库亦无监护仪高级参数表）</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>无数据源、无页面。已确认：监护仪 CO/SVR 未入库，本项走手工录入</t>
+          <t>2026-10-15落地：血流动力学手工录入模块（patient_doc_hemodynamics 表 + /api/hemodynamics/*），录入 SBP/DBP/MAP/CVP/CO，MAP 缺省按 DBP+(SBP-DBP)/3 补算、SVR=(MAP-CVP)/CO×80 服务端自动计算，多 y 轴趋势图（压力/CO/SVR+EF）+ 明细表 + 编辑删除</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4668,17 +4577,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>全库无 EF/射血分数/心功能分析实现（FE 命中 0）</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>无数据源（超声 EF 未入库）、无页面</t>
+          <t>2026-10-15落地：心功能（EF 射血分数）随血流动力学模块手工录入并趋势展示（源系统无 CO/CVP/EF 结构化数据，docs/25 §3 连库核查结论；页面标注「EF 仅展示，不做心衰结论」），测量方式区分 PiCCO / Swan-Ganz / 床旁超声</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4878,17 +4782,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>体温曲线、WBC、PCT 数据可经 labtrend（LIS）与体征数据获取；LabTrend 支持 lab-liver / lab-coag 两类面板</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>无「感染控制分析」独立页面（无体温+WBC+PCT 联合趋势页）</t>
+          <t>2026-10-15落地：院感分析页 /page/infection-watch（sql/54 注册），体温（38℃标线）+ WBC/PCT/CRP/IL-6 感染指标联合趋势（/api/lab-trend?type=infection 新面板，按项目名匹配、排除体液标本白细胞），附检验明细表</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5043,17 +4942,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LAB_TREND_TYPES 仅有 lab-liver、lab-coag 两类；LIS 数据源齐备（patient_info_lis/config_lis_item）</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>缺 lab-renal 面板（肌酐/尿素氮/电解质）</t>
+          <t>已落地：lab-renal 肾功能与电解质趋势页（肌酐/尿素氮/钾钠氯钙镁磷，sql/49 注册），已排除降钙素原等同名异物</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5583,17 +5477,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>全库无床旁彩超/超声模块（彩超、超声、ultrasound 命中 0，仅文档提及）</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>8 个部位（肺/眼球/下腔静脉/腹部/膈肌/肾脏/心脏/血管）教学功能全无</t>
+          <t>2026-10-15落地：床旁超声教学静态页 /page/echo-teaching（sql/56 注册），八部位（肺部/眼球/下腔静脉/腹部/膈肌/肾脏/心脏/血管）各含检查目的/操作要点/正常异常判读/注意事项，支持关键词过滤；标注「仅供教学参考，正式诊断以超声科报告为准」</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5998,17 +5887,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ARDSMonitor 内无筛查相关实现；ARDS 域筛查类指标未落地</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>无全院 ARDS 智能筛查</t>
+          <t>2026-10-15落地：ARDS 全院筛查页 /page/ards-screen（sql/54 注册 + /api/ards/hospital-screen），按周期「在院或已出科」×诊断（ARDS/急性呼吸窘迫综合征）全院清单（不限于俯卧位模块），含在科/已出科/涉及科室汇总、关键字过滤、患者跳转；柏林定义分级与肺保护通气达标在 ARDS 监测页（氧合指数自动分级 轻度/中度/重度）</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6158,17 +6042,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>未见疼痛评分与镇痛医嘱的关联分析实现（评分与医嘱分属两类数据，未做关联）</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>无「疼痛评分 vs 镇痛药剂量/时点」对比分析</t>
+          <t>2026-10-15落地：镇痛镇静监测页新增「镇痛药使用与评分关联」区块（/api/workbench/patients/{id}/analgesia），同窗口列出阿片类执行医嘱（芬太尼/瑞芬/舒芬、吗啡、地佐辛等：药品/剂量/泵速/起止）与 NRS/CPOT 评分同轴对照</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">

--- a/docs/功能清单验收对照表.xlsx
+++ b/docs/功能清单验收对照表.xlsx
@@ -2682,7 +2682,6 @@
           <t>质控看板已有「自定义」周期档位（periodType=CUSTOM 起止日期，后端 PeriodRange.CUSTOM）；指标详情抽屉含患者明细四档视角（全部/分子/分母/未达标）——48h 重返（quality_22）在自定义周期下点分子即得重返病例清单（/api/quality/metric/patients），可结合患者字段分析特征</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>给质控查询加起止日期参数 + 48h 重返病例筛选入口（数据现成，成本低）</t>
@@ -2843,7 +2842,6 @@
           <t>2026-10-15统一组件后：Apache2 总览页接入 TimeRangeBar（本月/近30天/近90天/本年快捷档 + 任意起止日期），分布/平均预期死亡率可按任意区间分析；页内未单独展示实际死亡数与标化死亡指数（SMR 已由质控看板 quality_30/31 规则自动出数）</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>补实际死亡数录入/核对流程（或接入死亡转归字段做校验）</t>
@@ -3514,7 +3512,6 @@
           <t>2026-10-15落地：导管统计按日视图支持自定义起止区间（TimeRangeBar，本月/近7天/近30天/本年快捷档，后端 /api/tube/daily startDate/endDate，上限92天），日粒度统计三管新置/拔管/带出/非计划/24h再插管/在管数；留置天数与感染口径在月度视图（avgDays/totalDays/感染说明）</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>加起止日期查询；感染发生率待院感确诊录入（序号 107/109/111）后计算</t>
@@ -4122,14 +4119,10 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>评分/质控待办提醒机制存在（sql/36_workbench_score_todo_rule.sql：待办规则表 + 工作台待办）</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>仅站内待办/弹窗提醒；无短信、无院内通讯软件（HIS 消息）推送通道</t>
-        </is>
-      </c>
+          <t>2026-10-15升级：待办由「悬停气泡」扩展为「主动弹窗」——工作台加载后对本轮新出现的待办弹系统级 ElNotification（patientId+code 去重，处理掉再出现才重新弹，点击跳「今日待办」视图）；待办规则扩至 5 类（SOFA/APACHE/抗感染复评/ARDS 机械通气/GCS 降幅）。短信/院内通讯软件通道需外部网关，未接</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>如需短信/院内通讯推送，需对接院方消息网关（依赖集成）</t>
@@ -5927,19 +5920,15 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>院内提醒机制（待办/弹窗）已存在，可承载预警</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>无 ARDS 专项预警规则；无短信/院内通讯推送通道</t>
-        </is>
-      </c>
+          <t>2026-10-15落地：新增待办规则 ARDS_VENTILATED（patient_info.is_ards=1 且机械通气中，批量查询不 N+1、不受 24h 前置约束），待办徽章/悬停/主动弹窗三通道提醒，一键跳转 ARDS 监测页（氧合指数分级/肺保护通气/俯卧位记录）</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>筛查落地后接入待办提醒；外发通道需院方消息网关</t>
@@ -6242,19 +6231,15 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NeuroMonitor.vue GCS 趋势图已实现</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>GCS 异常变化的智能预警未见实现（无阈值预警规则）</t>
-        </is>
-      </c>
+          <t>2026-10-15落地：新增待办规则 GCS_DROP_2（今日 Z_ICU_GCS 正式文书中首查→最新数值总分下降 ≥2 分；插管 VT 记录口径不可比自动跳过，当日少于 2 条可评全记录不报警），待办/主动弹窗提醒并一键跳转神经监测页</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>加 GCS 下降阈值预警（如 24h 内下降 ≥2 分）并接入待办提醒</t>

--- a/docs/功能清单验收对照表.xlsx
+++ b/docs/功能清单验收对照表.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>quality_12「抗菌药物治疗前病原学送检率」等已 IMPL；fact_abx_culture；页面 DddOverview.vue</t>
+          <t>quality_12「抗菌药物治疗前病原学送检率」等已 IMPL；fact_abx_culture；页面 DddOverview.vue；2026-10-15落地：药敏与在用抗菌药个体对照（/api/antibiotic/patients/{patientId}/sensitivity-contrast）——在用药各自药敏结论+药敏敏感但未在用清单，决策页展示</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2284,17 +2284,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>驾驶舱已有「设备接入态势」面板（DepartmentCockpitServiceImpl.java:266 deviceOverview：呼吸机/监护仪接入台数）</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>无独立设备管理页：设备使用统计、分布状态、运行状态、维护信息均缺；源库 config_device / config_large_device / patient_device_history / icu_device_maintenance_record / icu_device_check_record 尚未接</t>
+          <t>2026-10-15落地：设备状态页 /page/device-status（sql/57 注册 + GET /api/department-cockpit/device-status），只读重症系统 config_device：设备编码/类型（监护仪/呼吸机/CRRT/ECMO）/科室/当前绑定患者（在科四类设备编码精确匹配）/采集连接状态（正在接收/已连接/初始化/停止/异常/未接入）/最近更新，顶部六卡汇总（配置/使用中/未绑定/接收/异常/未接入），类型筛选；科室权限与驾驶舱同套路；口径与驾驶舱「设备接入态势」同源。源系统无维护台账，页面明确不虚构维修/库存语义</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2834,12 +2829,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-15统一组件后：Apache2 总览页接入 TimeRangeBar（本月/近30天/近90天/本年快捷档 + 任意起止日期），分布/平均预期死亡率可按任意区间分析；页内未单独展示实际死亡数与标化死亡指数（SMR 已由质控看板 quality_30/31 规则自动出数）</t>
+          <t>2026-10-15统一组件后：Apache2 总览页接入 TimeRangeBar（本月/近30天/近90天/本年快捷档 + 任意起止日期），分布/平均预期死亡率可按任意区间分析；页内未单独展示实际死亡数与标化死亡指数（SMR 已由质控看板 quality_30/31 规则自动出数）；2026-10-15落地：Apache II 总览页新增实际死亡数与 SMR（标准化死亡比）统计卡——预测死亡数=每位患者最新一条评分 mortality_rate/100 求和，实际死亡=patient_info.out_vest_type=3（与 quality_16 同口径），查询失败降级留空</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2974,17 +2969,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>评分明细列表有（时间/项目/结果）；有 staffSignature.js（签名/工号）用于评分单与俯卧位记录</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>护士评分明细的「评分人员」展示需逐一核对（「评估人」FE 仅 4 处命中；「评分人」0 命中）</t>
+          <t>评分明细列表有（时间/项目/结果）；有 staffSignature.js（签名/工号）用于评分单与俯卧位记录；2026-10-15落地：Apache II 总览评分明细表新增「评分人员」列（create_by 经占位值过滤展示，unknown 等占位显示 —）</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3339,12 +3329,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-15落地：月度明细与导管类型管理均带危重等级标注（高/中/低，配置优先，默认气道/CVC=高、导尿管=中、其余=低）；「按危重等级分模块置顶展示」未做，如需可基于 riskLevel 字段扩展</t>
+          <t>2026-10-15落地：月度明细与导管类型管理均带危重等级标注（高/中/低，配置优先，默认气道/CVC=高、导尿管=中、其余=低）；「按危重等级分模块置顶展示」未做，如需可基于 riskLevel 字段扩展；2026-10-15落地：导管月度明细按危重等级 高→中→低 置顶排序（TubeStatsService.riskRank，配置行 TubeGroupConfig.riskLevel 优先、三管默认档兜底，同档稳定排序）</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4119,10 +4109,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-15升级：待办由「悬停气泡」扩展为「主动弹窗」——工作台加载后对本轮新出现的待办弹系统级 ElNotification（patientId+code 去重，处理掉再出现才重新弹，点击跳「今日待办」视图）；待办规则扩至 5 类（SOFA/APACHE/抗感染复评/ARDS 机械通气/GCS 降幅）。短信/院内通讯软件通道需外部网关，未接</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
+          <t>2026-10-15升级：待办由「悬停气泡」扩展为「主动弹窗」——工作台加载后对本轮新出现的待办弹系统级 ElNotification（patientId+code 去重，处理掉再出现才重新弹，点击跳「今日待办」视图）；待办规则扩至 5 类（SOFA/APACHE/抗感染复评/ARDS 机械通气/GCS 降幅）。短信/院内通讯软件通道需外部网关，未接；2026-10-15落地：工作台待办/弹窗预警新增 PRONE_OVERTIME（俯卧位超时）、RR_DEPRESSION（最新呼吸频率&lt;8 次/min）</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>短信/院内通讯通道未接（弹窗+待办拉取式已可用）</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>如需短信/院内通讯推送，需对接院方消息网关（依赖集成）</t>
@@ -4525,17 +4519,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>驾驶舱「器官支持」统计血管活性药使用人数；医嘱数据（patient_order）可用于明细</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>无血管活性药物专项分析（种类/剂量/时长与血流动力学联动）</t>
+          <t>驾驶舱「器官支持」统计血管活性药使用人数；医嘱数据（patient_order）可用于明细；2026-10-15落地：新增血管活性药分析页 /page/vasoactive-analysis（GET /api/vasoactive/patients/{patientId}/analysis）——执行链路时间轴含调速步骤、开立在用医嘱、MAP（无创/有创分通道）与乳酸双轴趋势；取数与 SOFA 循环项同源；sql/58 页面注册</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5170,17 +5159,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>体温数据在生命体征页（VitalSigns.vue）以曲线呈现；源库有 patient_temperature_tube_record、patient_temperature_event_record（多部位）</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>无独立体温分析页；多部位体温（腋温/肛温/膀胱温等）与体温事件（降温措施）未展开分析</t>
+          <t>体温数据在生命体征页（VitalSigns.vue）以曲线呈现；源库有 patient_temperature_tube_record、patient_temperature_event_record（多部位）；2026-10-15落地：ARDS 俯卧位监测字典新增多部位体温自动采集 5 项（腋温/肛温/口温/耳温/额温，观察项名称包含匹配，无配置规则回退内置关键字），呼吸频率 rr 原已内置</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5220,12 +5204,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>出入量趋势分析（BalanceTrend）已实现入量/出量/平衡；体重数据在体征记录中</t>
+          <t>出入量趋势分析（BalanceTrend）已实现入量/出量/平衡；体重数据在体征记录中；2026-10-15落地：体液平衡页头部新增体重展示（patient_info.weight 登记值）；肢体活动经 docs/21 生产库核查无对应文书/观察项，页面已明示口径不虚构</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>无「液体评分」（含体重变化）综合评估</t>
+          <t>无「液体评分」综合评估；肢体活动源系统无数据（已明示）</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5510,12 +5494,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>不适用（源系统未启用）</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-10-15落地：镇痛镇静页新增VAS区块（解析/展示/明细表，解析口径同NRS 0-10）；源文书编码Z_ICU_SCORE_VAS待确认，接入后出数</t>
+          <t>2026-10-15业务方确认：重症系统暂未使用 VAS 镇痛评分文书，不出数也无需再接。页面侧 VAS 区块保留（Z_ICU_SCORE_VAS 编码约定），源系统启用后仅需确认编码即可点亮；NRS 已实现</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5715,17 +5699,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ARDS 专项域 8 项指标已定义但未落地；ArdsProneList.vue 维护中重度 ARDS 患者清单并特别标识</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>柏林定义自动筛选规则未见明确实现（ARDSMonitor 内无筛查/柏林定义关键词）</t>
+          <t>2026-10-15业务方确认：柏林定义的质控语义已由氧合指数（OI）自动分级覆盖——ARDS 监测页按氧合指数自动分级轻度/中度/重度并特别标识，ARDS 全院筛查页按诊断清单化；视为已实现</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5760,17 +5739,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ArdsProneRecord.vue（开始/结束时间、持续时间、签名）+ ArdsProneList.vue；待办提醒机制存在（sql/36_workbench_score_todo_rule.sql）</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>俯卧位体位转换的专项智能提醒未见实现（现有提醒是评分/待办规则）</t>
+          <t>ArdsProneRecord.vue（开始/结束时间、持续时间、签名）+ ArdsProneList.vue；待办提醒机制存在（sql/36_workbench_score_todo_rule.sql）；2026-10-15落地：患者工作台新增 PRONE_OVERTIME 待办（俯卧位进行中起始超 16 小时未记录结束，提醒复位/终止，跳转俯卧位记录页）</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5835,17 +5809,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ARDSMonitor.vue 含肺保护性通气依从率（潮气量/PEEP/氧合）；俯卧位记录含氧合改善</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>俯卧位前后氧合改善的量化对比图未见（仅记录）</t>
+          <t>ARDSMonitor.vue 含肺保护性通气依从率（潮气量/PEEP/氧合）；俯卧位记录含氧合改善；2026-10-15落地：俯卧位记录页新增「呼吸参数对照（翻身前后）」卡——T0 翻身前 vs 俯卧位中各已采集时点，覆盖 RR/设定RR/潮气量/PEEP/FiO2/Ppeak/Pplat/氧合指数</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5928,7 +5897,6 @@
           <t>2026-10-15落地：新增待办规则 ARDS_VENTILATED（patient_info.is_ards=1 且机械通气中，批量查询不 N+1、不受 24h 前置约束），待办徽章/悬停/主动弹窗三通道提醒，一键跳转 ARDS 监测页（氧合指数分级/肺保护通气/俯卧位记录）</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>筛查落地后接入待办提醒；外发通道需院方消息网关</t>
@@ -5961,12 +5929,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>不适用（源系统未启用）</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-10-15落地：镇痛镇静页新增VAS区块（解析/展示/明细表，解析口径同NRS 0-10）；源文书编码Z_ICU_SCORE_VAS待确认，接入后出数</t>
+          <t>2026-10-15业务方确认：重症系统暂未使用 VAS 文书。NRS 已实现（镇痛镇静页），VAS 区块保留待源系统启用；多项标准化评估工具的「规范性/可比性」以 NRS + CPOT + CAM-ICU 承载</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6071,17 +6039,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CAM-ICU 谵妄评估已实现（CamPoint.java 评估项、SedationAssessMapper 取数、SedationMonitor.vue:165 展示）</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>无阈值预警规则（谵妄阳性、呼吸抑制未触发提醒）；镇痛并发症未与镇痛药剂量联动</t>
+          <t>CAM-ICU 谵妄评估已实现（CamPoint.java 评估项、SedationAssessMapper 取数、SedationMonitor.vue:165 展示）；2026-10-15落地：工作台 RR_DEPRESSION 待办预警（监护 oi_hxpl 最新一次&lt;8 次/min）；谵妄侧 CAM-ICU 评估已有</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6121,12 +6084,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NeuroMonitor.vue 面向急性脑损伤患者意识评估，有患者清单与标识；质控侧有意识评估率指标（quality_307/308/423/424）</t>
+          <t>NeuroMonitor.vue 面向急性脑损伤患者意识评估，有患者清单与标识；质控侧有意识评估率指标（quality_307/308/423/424）；2026-10-15落地：工作台 BRAIN_INJURY 打标——诊断文本含脑出血/脑梗死/颅脑损伤/脑挫伤/蛛网膜下腔出血/脑疝/颅内感染/脑病等关键字即标识（监测类标记不弹窗，跳转神经监测页）</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>未见按病因（创伤性脑损伤/脑卒中）自动分类与标识</t>
+          <t>按 ICD 精确病因细分未做（诊断关键字打标已可用）</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6161,12 +6124,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>部分实现</t>
+          <t>不适用（源系统未启用）</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-10-15落地：神经监测页新增FOUR区块（0-16，插管可评，2024版ICU-18认可GCS或FOUR）；源文书编码Z_ICU_FOUR待确认</t>
+          <t>2026-10-15业务方确认：重症系统暂未使用 FOUR 评分文书，不出数也无需再接。页面侧 FOUR 区块保留（Z_ICU_FOUR 编码约定），源系统启用后仅需确认编码即可点亮；GCS + 瞳孔 + ICP + 神志已实现</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6239,7 +6202,6 @@
           <t>2026-10-15落地：新增待办规则 GCS_DROP_2（今日 Z_ICU_GCS 正式文书中首查→最新数值总分下降 ≥2 分；插管 VT 记录口径不可比自动跳过，当日少于 2 条可评全记录不报警），待办/主动弹窗提醒并一键跳转神经监测页</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>加 GCS 下降阈值预警（如 24h 内下降 ≥2 分）并接入待办提醒</t>
